--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_5F82977463C85CFAEAEBB78CF37F07FAB65EC282" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FECCF5D-4998-4B79-934E-0D139CD1BF38}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_5F82977463C85CFAEAEBB78CF37F07FAB65EC282" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA6D6F6C-5CEA-43A2-B8F4-8AF392D2A6F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,48 +807,6 @@
   </cellStyleXfs>
   <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -891,14 +849,56 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -983,6 +983,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1173,683 +1177,746 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="A6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="16">
+      <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="16">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="16">
-        <v>3</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="16">
+      <c r="A11" s="2">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="16">
+      <c r="A12" s="2">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="4" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="4" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="4" t="s">
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="4" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="4" t="s">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="16">
+      <c r="A32" s="2">
         <v>1</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="16">
-        <v>3</v>
-      </c>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="2">
+        <v>3</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="16">
+      <c r="A34" s="2">
         <v>5</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
     </row>
     <row r="36" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="16">
+      <c r="A37" s="2">
         <v>1</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="16">
+      <c r="A38" s="2">
         <v>2</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="16">
-        <v>3</v>
-      </c>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="2">
+        <v>3</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="16">
+      <c r="A40" s="2">
         <v>4</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="16">
+      <c r="A41" s="2">
         <v>5</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
     </row>
     <row r="43" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="16">
+      <c r="A44" s="2">
         <v>1</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="16">
+      <c r="A45" s="2">
         <v>2</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="16">
-        <v>3</v>
-      </c>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="2">
+        <v>3</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="16">
+      <c r="A47" s="2">
         <v>4</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="16">
+      <c r="A48" s="2">
         <v>5</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
     </row>
     <row r="50" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
     </row>
     <row r="51" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
     </row>
     <row r="52" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
     </row>
     <row r="54" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="9" t="s">
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="9" t="s">
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="9" t="s">
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="9" t="s">
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
     </row>
     <row r="61" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
     </row>
     <row r="63" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
     </row>
     <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
     </row>
     <row r="65" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
     </row>
     <row r="66" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
     </row>
     <row r="68" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
     </row>
     <row r="69" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
     </row>
     <row r="71" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
     </row>
     <row r="72" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
     </row>
     <row r="73" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
     </row>
     <row r="74" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
     </row>
     <row r="75" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A75:F75"/>
@@ -1858,69 +1925,6 @@
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1952,910 +1956,1038 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
     </row>
     <row r="2" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="P2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="6">
         <v>47</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="6">
         <f t="shared" ref="G3:G22" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="7">
         <v>2</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="7">
         <v>1</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="7">
         <v>2</v>
       </c>
-      <c r="K3" s="21">
-        <v>3</v>
-      </c>
-      <c r="L3" s="22">
+      <c r="K3" s="7">
+        <v>3</v>
+      </c>
+      <c r="L3" s="8">
         <f t="shared" ref="L3:L22" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
         <v>1.7</v>
       </c>
-      <c r="M3" s="23" t="str">
+      <c r="M3" s="9" t="str">
         <f t="shared" ref="M3:M22" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="12">
         <v>23</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H4" s="21">
-        <v>4</v>
-      </c>
-      <c r="I4" s="21">
+      <c r="H4" s="7">
+        <v>2</v>
+      </c>
+      <c r="I4" s="7">
+        <v>5</v>
+      </c>
+      <c r="J4" s="7">
         <v>1</v>
       </c>
-      <c r="J4" s="21">
+      <c r="K4" s="7">
         <v>2</v>
       </c>
-      <c r="K4" s="21">
-        <v>3</v>
-      </c>
-      <c r="L4" s="27">
+      <c r="L4" s="13">
+        <f t="shared" si="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="M4" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+    </row>
+    <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="6">
+        <v>43</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7">
+        <v>3</v>
+      </c>
+      <c r="K5" s="7">
+        <v>3</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
+      </c>
+      <c r="M5" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+    </row>
+    <row r="6" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="12">
+        <v>44</v>
+      </c>
+      <c r="G6" s="12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>2</v>
+      </c>
+      <c r="K6" s="7">
+        <v>3</v>
+      </c>
+      <c r="L6" s="13">
         <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
-      <c r="M4" s="28" t="str">
+      <c r="M6" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="6">
+        <v>41</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4</v>
+      </c>
+      <c r="I7" s="7">
+        <v>3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>4</v>
+      </c>
+      <c r="K7" s="7">
+        <v>3</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="1"/>
+        <v>2.9</v>
+      </c>
+      <c r="M7" s="9" t="str">
         <f t="shared" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-    </row>
-    <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="20">
-        <v>43</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="12">
+        <v>46</v>
+      </c>
+      <c r="G8" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H8" s="7">
         <v>4</v>
       </c>
-      <c r="I5" s="21">
-        <v>3</v>
-      </c>
-      <c r="J5" s="21">
-        <v>3</v>
-      </c>
-      <c r="K5" s="21">
+      <c r="I8" s="7">
+        <v>3</v>
+      </c>
+      <c r="J8" s="7">
         <v>4</v>
       </c>
-      <c r="L5" s="22">
+      <c r="K8" s="7">
+        <v>3</v>
+      </c>
+      <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>2.8</v>
-      </c>
-      <c r="M5" s="23" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M8" s="14" t="str">
         <f t="shared" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-    </row>
-    <row r="6" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" s="26">
-        <v>44</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+    </row>
+    <row r="9" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46</v>
+      </c>
+      <c r="G9" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H6" s="21">
-        <v>5</v>
-      </c>
-      <c r="I6" s="21">
-        <v>1</v>
-      </c>
-      <c r="J6" s="21">
-        <v>3</v>
-      </c>
-      <c r="K6" s="21">
-        <v>5</v>
-      </c>
-      <c r="L6" s="27">
+      <c r="H9" s="7">
+        <v>4</v>
+      </c>
+      <c r="I9" s="7">
+        <v>3</v>
+      </c>
+      <c r="J9" s="7">
+        <v>4</v>
+      </c>
+      <c r="K9" s="7">
+        <v>3</v>
+      </c>
+      <c r="L9" s="8">
         <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="M6" s="28" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M9" s="9" t="str">
         <f t="shared" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-    </row>
-    <row r="7" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="12">
+        <v>55</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H10" s="7">
+        <v>5</v>
+      </c>
+      <c r="I10" s="7">
+        <v>5</v>
+      </c>
+      <c r="J10" s="7">
+        <v>4</v>
+      </c>
+      <c r="K10" s="7">
+        <v>4</v>
+      </c>
+      <c r="L10" s="13">
+        <f t="shared" si="1"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M10" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+    </row>
+    <row r="11" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="20">
-        <v>41</v>
-      </c>
-      <c r="G7" s="20">
+      <c r="E11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="6">
+        <v>39</v>
+      </c>
+      <c r="G11" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22" t="str">
+      <c r="H11" s="7">
+        <v>4</v>
+      </c>
+      <c r="I11" s="7">
+        <v>3</v>
+      </c>
+      <c r="J11" s="7">
+        <v>4</v>
+      </c>
+      <c r="K11" s="7">
+        <v>3</v>
+      </c>
+      <c r="L11" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M7" s="23" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M11" s="9" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-    </row>
-    <row r="8" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="24" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="26">
-        <v>46</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="E12" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="12">
+        <v>39</v>
+      </c>
+      <c r="G12" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="27" t="str">
+      <c r="H12" s="7">
+        <v>4</v>
+      </c>
+      <c r="I12" s="7">
+        <v>3</v>
+      </c>
+      <c r="J12" s="7">
+        <v>5</v>
+      </c>
+      <c r="K12" s="7">
+        <v>4</v>
+      </c>
+      <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M8" s="28" t="str">
+        <v>3.4</v>
+      </c>
+      <c r="M12" s="14" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-    </row>
-    <row r="9" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" s="20">
-        <v>46</v>
-      </c>
-      <c r="G9" s="20">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+    </row>
+    <row r="13" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="6">
+        <v>54</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
+        <v>5</v>
+      </c>
+      <c r="J13" s="7">
+        <v>5</v>
+      </c>
+      <c r="K13" s="7">
+        <v>4</v>
+      </c>
+      <c r="L13" s="8">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+      <c r="M13" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Low Impact + High Risk</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="12">
+        <v>49</v>
+      </c>
+      <c r="G14" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="22" t="str">
+      <c r="H14" s="7">
+        <v>4</v>
+      </c>
+      <c r="I14" s="7">
+        <v>5</v>
+      </c>
+      <c r="J14" s="7">
+        <v>5</v>
+      </c>
+      <c r="K14" s="7">
+        <v>4</v>
+      </c>
+      <c r="L14" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M9" s="23" t="str">
+        <v>4</v>
+      </c>
+      <c r="M14" s="14" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-    </row>
-    <row r="10" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="26">
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+    </row>
+    <row r="15" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="6">
+        <v>50</v>
+      </c>
+      <c r="G15" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3</v>
+      </c>
+      <c r="I15" s="7">
+        <v>5</v>
+      </c>
+      <c r="J15" s="7">
+        <v>5</v>
+      </c>
+      <c r="K15" s="7">
+        <v>4</v>
+      </c>
+      <c r="L15" s="8">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+      <c r="M15" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Low Impact + High Risk</v>
+      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="12">
         <v>55</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G16" s="12">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="27" t="str">
+      <c r="H16" s="7">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7">
+        <v>5</v>
+      </c>
+      <c r="J16" s="7">
+        <v>3</v>
+      </c>
+      <c r="K16" s="7">
+        <v>3</v>
+      </c>
+      <c r="L16" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M10" s="28" t="str">
+        <v>3.6</v>
+      </c>
+      <c r="M16" s="14" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-    </row>
-    <row r="11" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="20">
-        <v>39</v>
-      </c>
-      <c r="G11" s="20">
+        <v>Low Impact + High Risk</v>
+      </c>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="6">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22" t="str">
+      <c r="H17" s="7">
+        <v>3</v>
+      </c>
+      <c r="I17" s="7">
+        <v>3</v>
+      </c>
+      <c r="J17" s="7">
+        <v>4</v>
+      </c>
+      <c r="K17" s="7">
+        <v>3</v>
+      </c>
+      <c r="L17" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M11" s="23" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M17" s="9" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-    </row>
-    <row r="12" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="26">
-        <v>39</v>
-      </c>
-      <c r="G12" s="26">
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="12">
+        <v>43</v>
+      </c>
+      <c r="G18" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="27" t="str">
+      <c r="H18" s="7">
+        <v>2</v>
+      </c>
+      <c r="I18" s="7">
+        <v>3</v>
+      </c>
+      <c r="J18" s="7">
+        <v>4</v>
+      </c>
+      <c r="K18" s="7">
+        <v>3</v>
+      </c>
+      <c r="L18" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M12" s="28" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M18" s="14" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-    </row>
-    <row r="13" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="20">
-        <v>54</v>
-      </c>
-      <c r="G13" s="20">
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+    </row>
+    <row r="19" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="6">
+        <v>51</v>
+      </c>
+      <c r="G19" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="22" t="str">
+      <c r="H19" s="7">
+        <v>4</v>
+      </c>
+      <c r="I19" s="7">
+        <v>5</v>
+      </c>
+      <c r="J19" s="7">
+        <v>4</v>
+      </c>
+      <c r="K19" s="7">
+        <v>3</v>
+      </c>
+      <c r="L19" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M13" s="23" t="str">
+        <v>3.7</v>
+      </c>
+      <c r="M19" s="9" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-    </row>
-    <row r="14" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F14" s="26">
-        <v>49</v>
-      </c>
-      <c r="G14" s="26">
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="12">
+        <v>52</v>
+      </c>
+      <c r="G20" s="12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H20" s="7">
+        <v>5</v>
+      </c>
+      <c r="I20" s="7">
+        <v>5</v>
+      </c>
+      <c r="J20" s="7">
+        <v>4</v>
+      </c>
+      <c r="K20" s="7">
+        <v>3</v>
+      </c>
+      <c r="L20" s="13">
+        <f t="shared" si="1"/>
+        <v>3.7</v>
+      </c>
+      <c r="M20" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+    </row>
+    <row r="21" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F21" s="6">
+        <v>56</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H21" s="7">
+        <v>5</v>
+      </c>
+      <c r="I21" s="7">
+        <v>5</v>
+      </c>
+      <c r="J21" s="7">
+        <v>4</v>
+      </c>
+      <c r="K21" s="7">
+        <v>3</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+      <c r="M21" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="12">
+        <v>32</v>
+      </c>
+      <c r="G22" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="27" t="str">
+      <c r="H22" s="7">
+        <v>4</v>
+      </c>
+      <c r="I22" s="7">
+        <v>3</v>
+      </c>
+      <c r="J22" s="7">
+        <v>4</v>
+      </c>
+      <c r="K22" s="7">
+        <v>3</v>
+      </c>
+      <c r="L22" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M14" s="28" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M22" s="14" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-    </row>
-    <row r="15" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="20">
-        <v>50</v>
-      </c>
-      <c r="G15" s="20">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M15" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-    </row>
-    <row r="16" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="26">
-        <v>55</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M16" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-    </row>
-    <row r="17" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="F17" s="20">
-        <v>48</v>
-      </c>
-      <c r="G17" s="20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M17" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-    </row>
-    <row r="18" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="F18" s="26">
-        <v>43</v>
-      </c>
-      <c r="G18" s="26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M18" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-    </row>
-    <row r="19" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="20">
-        <v>51</v>
-      </c>
-      <c r="G19" s="20">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M19" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-    </row>
-    <row r="20" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F20" s="26">
-        <v>52</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M20" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-    </row>
-    <row r="21" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="F21" s="20">
-        <v>56</v>
-      </c>
-      <c r="G21" s="20">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M21" s="23" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-    </row>
-    <row r="22" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="F22" s="26">
-        <v>32</v>
-      </c>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M22" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A250A29B-AC82-406E-AC96-2CF0EDEDA93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D301880-71A8-47F5-9FF0-BDDE8C77C177}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61D018CE-E0EB-4948-AD36-C7854ADED339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$48</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -937,43 +937,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -984,6 +960,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1259,727 +1259,693 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29" t="s">
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="29"/>
+      <c r="G26" s="32"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="29" t="s">
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="29"/>
+      <c r="G27" s="32"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="32"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="29" t="s">
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="29"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29" t="s">
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="29"/>
+      <c r="G30" s="32"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="26" t="s">
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="26" t="s">
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="34" t="s">
+      <c r="B58" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="26" t="s">
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="26" t="s">
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="24" t="s">
+      <c r="B63" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="24" t="s">
+      <c r="B71" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="24" t="s">
+      <c r="B72" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="24" t="s">
+      <c r="B73" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="24" t="s">
+      <c r="B75" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -1993,18 +1959,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="F8" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -2622,17 +2622,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="18" t="str">
+      <c r="H14" s="12">
+        <v>4</v>
+      </c>
+      <c r="I14" s="12">
+        <v>5</v>
+      </c>
+      <c r="J14" s="12">
+        <v>4</v>
+      </c>
+      <c r="K14" s="12">
+        <v>5</v>
+      </c>
+      <c r="L14" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.9</v>
       </c>
       <c r="M14" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + High Risk</v>
       </c>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
@@ -2666,17 +2674,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13" t="str">
+      <c r="H15" s="12">
+        <v>4</v>
+      </c>
+      <c r="I15" s="12">
+        <v>3</v>
+      </c>
+      <c r="J15" s="12">
+        <v>4</v>
+      </c>
+      <c r="K15" s="12">
+        <v>3</v>
+      </c>
+      <c r="L15" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="M15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
@@ -2710,17 +2726,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="18" t="str">
+      <c r="H16" s="12">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12">
+        <v>1</v>
+      </c>
+      <c r="J16" s="12">
+        <v>3</v>
+      </c>
+      <c r="K16" s="12">
+        <v>4</v>
+      </c>
+      <c r="L16" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="M16" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -2754,17 +2778,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="13" t="str">
+      <c r="H17" s="12">
+        <v>3</v>
+      </c>
+      <c r="I17" s="12">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12">
+        <v>4</v>
+      </c>
+      <c r="K17" s="12">
+        <v>4</v>
+      </c>
+      <c r="L17" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.7</v>
       </c>
       <c r="M17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
@@ -2798,17 +2830,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="18" t="str">
+      <c r="H18" s="12">
+        <v>3</v>
+      </c>
+      <c r="I18" s="12">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12">
+        <v>3</v>
+      </c>
+      <c r="K18" s="12">
+        <v>3</v>
+      </c>
+      <c r="L18" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="M18" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
@@ -2886,17 +2926,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="13" t="str">
+      <c r="H20" s="12">
+        <v>3</v>
+      </c>
+      <c r="I20" s="12">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12">
+        <v>4</v>
+      </c>
+      <c r="K20" s="12">
+        <v>4</v>
+      </c>
+      <c r="L20" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="M20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
@@ -2930,17 +2978,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="18" t="str">
+      <c r="H21" s="12">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12">
+        <v>3</v>
+      </c>
+      <c r="K21" s="12">
+        <v>3</v>
+      </c>
+      <c r="L21" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M21" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
@@ -2974,17 +3030,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="13" t="str">
+      <c r="H22" s="12">
+        <v>3</v>
+      </c>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>3</v>
+      </c>
+      <c r="K22" s="12">
+        <v>3</v>
+      </c>
+      <c r="L22" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="M22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N22" s="9"/>
       <c r="O22" s="9"/>
@@ -3018,17 +3082,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="18" t="str">
+      <c r="H23" s="12">
+        <v>4</v>
+      </c>
+      <c r="I23" s="12">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>4</v>
+      </c>
+      <c r="K23" s="12">
+        <v>4</v>
+      </c>
+      <c r="L23" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.7</v>
       </c>
       <c r="M23" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
@@ -3062,17 +3134,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="13" t="str">
+      <c r="H24" s="12">
+        <v>3</v>
+      </c>
+      <c r="I24" s="12">
+        <v>1</v>
+      </c>
+      <c r="J24" s="12">
+        <v>3</v>
+      </c>
+      <c r="K24" s="12">
+        <v>4</v>
+      </c>
+      <c r="L24" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.6</v>
       </c>
       <c r="M24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
@@ -3106,17 +3186,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="18" t="str">
+      <c r="H25" s="12">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12">
+        <v>3</v>
+      </c>
+      <c r="J25" s="12">
+        <v>3</v>
+      </c>
+      <c r="K25" s="12">
+        <v>4</v>
+      </c>
+      <c r="L25" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.8</v>
       </c>
       <c r="M25" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
@@ -3150,17 +3238,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="13" t="str">
+      <c r="H26" s="12">
+        <v>3</v>
+      </c>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12">
+        <v>4</v>
+      </c>
+      <c r="K26" s="12">
+        <v>4</v>
+      </c>
+      <c r="L26" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.7</v>
       </c>
       <c r="M26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
@@ -3194,17 +3290,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="18" t="str">
+      <c r="H27" s="12">
+        <v>3</v>
+      </c>
+      <c r="I27" s="12">
+        <v>5</v>
+      </c>
+      <c r="J27" s="12">
+        <v>4</v>
+      </c>
+      <c r="K27" s="12">
+        <v>4</v>
+      </c>
+      <c r="L27" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.7</v>
       </c>
       <c r="M27" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + High Risk</v>
       </c>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
@@ -3238,17 +3342,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="13" t="str">
+      <c r="H28" s="12">
+        <v>3</v>
+      </c>
+      <c r="I28" s="12">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12">
+        <v>3</v>
+      </c>
+      <c r="K28" s="12">
+        <v>4</v>
+      </c>
+      <c r="L28" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="M28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N28" s="9"/>
       <c r="O28" s="9"/>
@@ -3282,17 +3394,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="18" t="str">
+      <c r="H29" s="12">
+        <v>4</v>
+      </c>
+      <c r="I29" s="12">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12">
+        <v>4</v>
+      </c>
+      <c r="K29" s="12">
+        <v>4</v>
+      </c>
+      <c r="L29" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M29" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
@@ -3326,17 +3446,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="13" t="str">
+      <c r="H30" s="12">
+        <v>4</v>
+      </c>
+      <c r="I30" s="12">
+        <v>1</v>
+      </c>
+      <c r="J30" s="12">
+        <v>4</v>
+      </c>
+      <c r="K30" s="12">
+        <v>5</v>
+      </c>
+      <c r="L30" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.7</v>
       </c>
       <c r="M30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
@@ -3370,17 +3498,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="18" t="str">
+      <c r="H31" s="12">
+        <v>4</v>
+      </c>
+      <c r="I31" s="12">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12">
+        <v>4</v>
+      </c>
+      <c r="K31" s="12">
+        <v>4</v>
+      </c>
+      <c r="L31" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M31" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
@@ -3414,17 +3550,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="13" t="str">
+      <c r="H32" s="12">
+        <v>4</v>
+      </c>
+      <c r="I32" s="12">
+        <v>1</v>
+      </c>
+      <c r="J32" s="12">
+        <v>4</v>
+      </c>
+      <c r="K32" s="12">
+        <v>5</v>
+      </c>
+      <c r="L32" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="M32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
@@ -3458,17 +3602,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="18" t="str">
+      <c r="H33" s="12">
+        <v>4</v>
+      </c>
+      <c r="I33" s="12">
+        <v>3</v>
+      </c>
+      <c r="J33" s="12">
+        <v>4</v>
+      </c>
+      <c r="K33" s="12">
+        <v>4</v>
+      </c>
+      <c r="L33" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="M33" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
@@ -3502,17 +3654,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="13" t="str">
+      <c r="H34" s="12">
+        <v>4</v>
+      </c>
+      <c r="I34" s="12">
+        <v>1</v>
+      </c>
+      <c r="J34" s="12">
+        <v>4</v>
+      </c>
+      <c r="K34" s="12">
+        <v>5</v>
+      </c>
+      <c r="L34" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.7</v>
       </c>
       <c r="M34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
@@ -3546,17 +3706,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="18" t="str">
+      <c r="H35" s="12">
+        <v>4</v>
+      </c>
+      <c r="I35" s="12">
+        <v>3</v>
+      </c>
+      <c r="J35" s="12">
+        <v>4</v>
+      </c>
+      <c r="K35" s="12">
+        <v>4</v>
+      </c>
+      <c r="L35" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="M35" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
@@ -3590,17 +3758,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="13" t="str">
+      <c r="H36" s="12">
+        <v>3</v>
+      </c>
+      <c r="I36" s="12">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12">
+        <v>3</v>
+      </c>
+      <c r="K36" s="12">
+        <v>4</v>
+      </c>
+      <c r="L36" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="M36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
@@ -3634,17 +3810,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="18" t="str">
+      <c r="H37" s="12">
+        <v>3</v>
+      </c>
+      <c r="I37" s="12">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12">
+        <v>4</v>
+      </c>
+      <c r="K37" s="12">
+        <v>4</v>
+      </c>
+      <c r="L37" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="M37" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
@@ -3678,17 +3862,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="13" t="str">
+      <c r="H38" s="12">
+        <v>4</v>
+      </c>
+      <c r="I38" s="12">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12">
+        <v>3</v>
+      </c>
+      <c r="K38" s="12">
+        <v>4</v>
+      </c>
+      <c r="L38" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="M38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N38" s="9"/>
       <c r="O38" s="9"/>
@@ -3722,17 +3914,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="18" t="str">
+      <c r="H39" s="12">
+        <v>3</v>
+      </c>
+      <c r="I39" s="12">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12">
+        <v>5</v>
+      </c>
+      <c r="L39" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.7</v>
       </c>
       <c r="M39" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N39" s="15"/>
       <c r="O39" s="15"/>
@@ -3766,17 +3966,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="13" t="str">
+      <c r="H40" s="12">
+        <v>4</v>
+      </c>
+      <c r="I40" s="12">
+        <v>3</v>
+      </c>
+      <c r="J40" s="12">
+        <v>4</v>
+      </c>
+      <c r="K40" s="12">
+        <v>4</v>
+      </c>
+      <c r="L40" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="M40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
@@ -3810,17 +4018,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="18" t="str">
+      <c r="H41" s="12">
+        <v>3</v>
+      </c>
+      <c r="I41" s="12">
+        <v>1</v>
+      </c>
+      <c r="J41" s="12">
+        <v>3</v>
+      </c>
+      <c r="K41" s="12">
+        <v>4</v>
+      </c>
+      <c r="L41" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="M41" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N41" s="15"/>
       <c r="O41" s="15"/>
@@ -3848,7 +4064,7 @@
       </c>
       <c r="F42" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G42" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -4181,7 +4397,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S48" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61D018CE-E0EB-4948-AD36-C7854ADED339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{47DEDFC0-AFDC-4FD9-AFD0-8574978C772A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A976172-9FE9-49DC-963A-233582E0C4D6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$49</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="200">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -412,12 +412,6 @@
     <t>Section Manager - Talent Acquisition &amp; Learning Development</t>
   </si>
   <si>
-    <t>นฤพนธ์ ชูชีพ</t>
-  </si>
-  <si>
-    <t>Senior Officer - Employee Experience</t>
-  </si>
-  <si>
     <t>วัชระ สะติรัน</t>
   </si>
   <si>
@@ -620,6 +614,30 @@
   </si>
   <si>
     <t>ผู้สืบทอดภายในอาจจะพร้อม 3+years</t>
+  </si>
+  <si>
+    <t>รักดี ภักดีชุมพล</t>
+  </si>
+  <si>
+    <t>Corporate Secretary &amp; Director of Corporate Affairs</t>
+  </si>
+  <si>
+    <t>23/12/1974</t>
+  </si>
+  <si>
+    <t>รุจิราพร คงสวัสดิ์</t>
+  </si>
+  <si>
+    <t>Manager - Industry Relation</t>
+  </si>
+  <si>
+    <t>06/08/1960</t>
+  </si>
+  <si>
+    <t>สิรภพ</t>
+  </si>
+  <si>
+    <t>Ready in 3 Years</t>
   </si>
 </sst>
 </file>
@@ -937,19 +955,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -960,30 +1002,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1068,6 +1086,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1259,693 +1281,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="32"/>
+      <c r="G26" s="29"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32" t="s">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="32"/>
+      <c r="G27" s="29"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32" t="s">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="32"/>
+      <c r="G28" s="29"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32" t="s">
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="32"/>
+      <c r="G29" s="29"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32" t="s">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="29"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="24" t="s">
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="24" t="s">
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="26" t="s">
+      <c r="B58" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="24" t="s">
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="24" t="s">
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="20" t="s">
+      <c r="B74" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -1959,52 +2015,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2013,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2135,7 +2157,7 @@
         <v>41</v>
       </c>
       <c r="G3" s="11">
-        <f t="shared" ref="G3:G48" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
+        <f t="shared" ref="G3:G49" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
         <v>1</v>
       </c>
       <c r="H3" s="12"/>
@@ -2143,11 +2165,11 @@
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
       <c r="L3" s="13" t="str">
-        <f t="shared" ref="L3:L48" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
+        <f t="shared" ref="L3:L49" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
         <v/>
       </c>
       <c r="M3" s="13" t="str">
-        <f t="shared" ref="M3:M48" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M3:M49" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v/>
       </c>
       <c r="N3" s="9"/>
@@ -2175,7 +2197,7 @@
         <v>29304</v>
       </c>
       <c r="F4" s="17">
-        <f t="shared" ref="F4:F48" ca="1" si="3">DATEDIF(E4,TODAY(),"Y")</f>
+        <f t="shared" ref="F4:F49" ca="1" si="3">DATEDIF(E4,TODAY(),"Y")</f>
         <v>46</v>
       </c>
       <c r="G4" s="17">
@@ -2264,7 +2286,7 @@
       </c>
       <c r="F6" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -2446,17 +2468,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13" t="str">
+      <c r="H10" s="12">
+        <v>2</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12">
+        <v>2</v>
+      </c>
+      <c r="K10" s="12">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="M10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
@@ -2490,17 +2520,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="18" t="str">
+      <c r="H11" s="12">
+        <v>4</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12">
+        <v>3</v>
+      </c>
+      <c r="K11" s="12">
+        <v>2</v>
+      </c>
+      <c r="L11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>1.8</v>
       </c>
       <c r="M11" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
@@ -2534,17 +2572,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13" t="str">
+      <c r="H12" s="12">
+        <v>3</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M12" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
@@ -2556,39 +2602,45 @@
     </row>
     <row r="13" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
-        <v>168018</v>
+        <v>466004</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="16">
-        <v>33417</v>
+      <c r="E13" s="16" t="s">
+        <v>197</v>
       </c>
       <c r="F13" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="G13" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="18" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="H13" s="12">
+        <v>4</v>
+      </c>
+      <c r="I13" s="12">
+        <v>5</v>
+      </c>
+      <c r="J13" s="12">
+        <v>3</v>
+      </c>
+      <c r="K13" s="12">
+        <v>3</v>
+      </c>
+      <c r="L13" s="18">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="M13" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>High Impact + High Risk</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
@@ -2599,1818 +2651,1902 @@
       </c>
     </row>
     <row r="14" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
+        <v>159029</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F14" s="11">
+        <v>52</v>
+      </c>
+      <c r="G14" s="11">
+        <v>2</v>
+      </c>
+      <c r="H14" s="12">
+        <v>5</v>
+      </c>
+      <c r="I14" s="12">
+        <v>1</v>
+      </c>
+      <c r="J14" s="12">
+        <v>2</v>
+      </c>
+      <c r="K14" s="12">
+        <v>5</v>
+      </c>
+      <c r="L14" s="13">
+        <f t="shared" ref="L14" si="4">IF(OR(I14="",J14="",K14="",G14=""),"",ROUND(G14*0.2+I14*0.3+J14*0.3+K14*0.2,2))</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M14" s="13" t="str">
+        <f t="shared" ref="M14" si="5">IF(OR(H14="",L14=""),"",IF(AND(H14&gt;=4,L14&gt;=3.5),"High Impact + High Risk",IF(AND(H14&gt;=4,L14&lt;3.5),"High Impact + Low Risk",IF(AND(H14&lt;4,L14&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="S14" s="7"/>
+    </row>
+    <row r="15" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
         <v>264090</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="B15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E15" s="16">
         <v>31762</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>39</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G15" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H14" s="12">
-        <v>4</v>
-      </c>
-      <c r="I14" s="12">
+      <c r="H15" s="12">
+        <v>4</v>
+      </c>
+      <c r="I15" s="12">
         <v>5</v>
       </c>
-      <c r="J14" s="12">
-        <v>4</v>
-      </c>
-      <c r="K14" s="12">
+      <c r="J15" s="12">
+        <v>4</v>
+      </c>
+      <c r="K15" s="12">
         <v>5</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L15" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>3.9</v>
       </c>
-      <c r="M14" s="18" t="str">
+      <c r="M15" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="S14" s="8" t="s">
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="S15" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>239006</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
-        <v>239006</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E16" s="10">
         <v>26179</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F16" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>54</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G16" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H15" s="12">
-        <v>4</v>
-      </c>
-      <c r="I15" s="12">
-        <v>3</v>
-      </c>
-      <c r="J15" s="12">
-        <v>4</v>
-      </c>
-      <c r="K15" s="12">
-        <v>3</v>
-      </c>
-      <c r="L15" s="13">
+      <c r="H16" s="12">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12">
+        <v>3</v>
+      </c>
+      <c r="J16" s="12">
+        <v>4</v>
+      </c>
+      <c r="K16" s="12">
+        <v>3</v>
+      </c>
+      <c r="L16" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M15" s="13" t="str">
+      <c r="M16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="S15" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="S16" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
         <v>246004</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="15" t="s">
+      <c r="B17" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E17" s="16">
         <v>28270</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F17" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G17" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="12">
-        <v>4</v>
-      </c>
-      <c r="I16" s="12">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12">
-        <v>3</v>
-      </c>
-      <c r="K16" s="12">
-        <v>4</v>
-      </c>
-      <c r="L16" s="18">
+      <c r="H17" s="12">
+        <v>4</v>
+      </c>
+      <c r="I17" s="12">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12">
+        <v>3</v>
+      </c>
+      <c r="K17" s="12">
+        <v>4</v>
+      </c>
+      <c r="L17" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M16" s="18" t="str">
+      <c r="M17" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="S16" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="S17" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
         <v>242032</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="B18" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E18" s="10">
         <v>27745</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F18" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>50</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G18" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H17" s="12">
-        <v>3</v>
-      </c>
-      <c r="I17" s="12">
-        <v>1</v>
-      </c>
-      <c r="J17" s="12">
-        <v>4</v>
-      </c>
-      <c r="K17" s="12">
-        <v>4</v>
-      </c>
-      <c r="L17" s="13">
+      <c r="H18" s="12">
+        <v>3</v>
+      </c>
+      <c r="I18" s="12">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12">
+        <v>4</v>
+      </c>
+      <c r="K18" s="12">
+        <v>4</v>
+      </c>
+      <c r="L18" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M17" s="13" t="str">
+      <c r="M18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="S17" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="S18" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
         <v>149024</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="B19" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E19" s="16">
         <v>26070</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F19" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>55</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G19" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H18" s="12">
-        <v>3</v>
-      </c>
-      <c r="I18" s="12">
-        <v>1</v>
-      </c>
-      <c r="J18" s="12">
-        <v>3</v>
-      </c>
-      <c r="K18" s="12">
-        <v>3</v>
-      </c>
-      <c r="L18" s="18">
+      <c r="H19" s="12">
+        <v>3</v>
+      </c>
+      <c r="I19" s="12">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12">
+        <v>3</v>
+      </c>
+      <c r="K19" s="12">
+        <v>3</v>
+      </c>
+      <c r="L19" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="M18" s="18" t="str">
+      <c r="M19" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="S18" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="16">
-        <v>27122</v>
-      </c>
-      <c r="F19" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="G19" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="18" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M19" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
       <c r="S19" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+      <c r="A20" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="16">
+        <v>27122</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="G20" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="18" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M20" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="S20" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
         <v>232027</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E21" s="10">
         <v>24838</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F21" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>58</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G21" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="H20" s="12">
-        <v>3</v>
-      </c>
-      <c r="I20" s="12">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12">
-        <v>4</v>
-      </c>
-      <c r="K20" s="12">
-        <v>4</v>
-      </c>
-      <c r="L20" s="13">
+      <c r="H21" s="12">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12">
+        <v>4</v>
+      </c>
+      <c r="K21" s="12">
+        <v>4</v>
+      </c>
+      <c r="L21" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M20" s="13" t="str">
+      <c r="M21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="S20" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="S21" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
         <v>256029</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="B22" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E22" s="16">
         <v>31119</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F22" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>41</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G22" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="12">
-        <v>3</v>
-      </c>
-      <c r="I21" s="12">
-        <v>1</v>
-      </c>
-      <c r="J21" s="12">
-        <v>3</v>
-      </c>
-      <c r="K21" s="12">
-        <v>3</v>
-      </c>
-      <c r="L21" s="18">
+      <c r="H22" s="12">
+        <v>3</v>
+      </c>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>3</v>
+      </c>
+      <c r="K22" s="12">
+        <v>3</v>
+      </c>
+      <c r="L22" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="M21" s="18" t="str">
+      <c r="M22" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="S21" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="S22" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
         <v>236012</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="B23" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E23" s="10">
         <v>26421</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F23" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>54</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G23" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H22" s="12">
-        <v>3</v>
-      </c>
-      <c r="I22" s="12">
-        <v>1</v>
-      </c>
-      <c r="J22" s="12">
-        <v>3</v>
-      </c>
-      <c r="K22" s="12">
-        <v>3</v>
-      </c>
-      <c r="L22" s="13">
+      <c r="H23" s="12">
+        <v>3</v>
+      </c>
+      <c r="I23" s="12">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>3</v>
+      </c>
+      <c r="K23" s="12">
+        <v>3</v>
+      </c>
+      <c r="L23" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M22" s="13" t="str">
+      <c r="M23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="S22" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8">
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="S23" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
         <v>250042</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="B24" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E24" s="16">
         <v>26738</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F24" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>53</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G24" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H23" s="12">
-        <v>4</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1</v>
-      </c>
-      <c r="J23" s="12">
-        <v>4</v>
-      </c>
-      <c r="K23" s="12">
-        <v>4</v>
-      </c>
-      <c r="L23" s="18">
+      <c r="H24" s="12">
+        <v>4</v>
+      </c>
+      <c r="I24" s="12">
+        <v>1</v>
+      </c>
+      <c r="J24" s="12">
+        <v>4</v>
+      </c>
+      <c r="K24" s="12">
+        <v>4</v>
+      </c>
+      <c r="L24" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M23" s="18" t="str">
+      <c r="M24" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="S23" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="S24" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
         <v>233034</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="B25" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E25" s="10">
         <v>25245</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F25" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>57</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G25" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H24" s="12">
-        <v>3</v>
-      </c>
-      <c r="I24" s="12">
-        <v>1</v>
-      </c>
-      <c r="J24" s="12">
-        <v>3</v>
-      </c>
-      <c r="K24" s="12">
-        <v>4</v>
-      </c>
-      <c r="L24" s="13">
+      <c r="H25" s="12">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12">
+        <v>3</v>
+      </c>
+      <c r="K25" s="12">
+        <v>4</v>
+      </c>
+      <c r="L25" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.6</v>
       </c>
-      <c r="M24" s="13" t="str">
+      <c r="M25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="S24" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8">
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="S25" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
         <v>268013</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="B26" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E26" s="16">
         <v>29244</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F26" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>46</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G26" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H25" s="12">
-        <v>3</v>
-      </c>
-      <c r="I25" s="12">
-        <v>3</v>
-      </c>
-      <c r="J25" s="12">
-        <v>3</v>
-      </c>
-      <c r="K25" s="12">
-        <v>4</v>
-      </c>
-      <c r="L25" s="18">
+      <c r="H26" s="12">
+        <v>3</v>
+      </c>
+      <c r="I26" s="12">
+        <v>3</v>
+      </c>
+      <c r="J26" s="12">
+        <v>3</v>
+      </c>
+      <c r="K26" s="12">
+        <v>4</v>
+      </c>
+      <c r="L26" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.8</v>
       </c>
-      <c r="M25" s="18" t="str">
+      <c r="M26" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="S25" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="7">
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="S26" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
         <v>249010</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="B27" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E27" s="10">
         <v>27467</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F27" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>51</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G27" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H26" s="12">
-        <v>3</v>
-      </c>
-      <c r="I26" s="12">
-        <v>1</v>
-      </c>
-      <c r="J26" s="12">
-        <v>4</v>
-      </c>
-      <c r="K26" s="12">
-        <v>4</v>
-      </c>
-      <c r="L26" s="13">
+      <c r="H27" s="12">
+        <v>3</v>
+      </c>
+      <c r="I27" s="12">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12">
+        <v>4</v>
+      </c>
+      <c r="K27" s="12">
+        <v>4</v>
+      </c>
+      <c r="L27" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M26" s="13" t="str">
+      <c r="M27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="S26" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="S27" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
         <v>268012</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D27" s="15" t="s">
+      <c r="B28" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E28" s="16">
         <v>31704</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F28" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>39</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G28" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H27" s="12">
-        <v>3</v>
-      </c>
-      <c r="I27" s="12">
+      <c r="H28" s="12">
+        <v>3</v>
+      </c>
+      <c r="I28" s="12">
         <v>5</v>
       </c>
-      <c r="J27" s="12">
-        <v>4</v>
-      </c>
-      <c r="K27" s="12">
-        <v>4</v>
-      </c>
-      <c r="L27" s="18">
+      <c r="J28" s="12">
+        <v>4</v>
+      </c>
+      <c r="K28" s="12">
+        <v>4</v>
+      </c>
+      <c r="L28" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>3.7</v>
       </c>
-      <c r="M27" s="18" t="str">
+      <c r="M28" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + High Risk</v>
       </c>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="S27" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="S28" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
         <v>238030</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="B29" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E29" s="10">
         <v>27404</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F29" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>51</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G29" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H28" s="12">
-        <v>3</v>
-      </c>
-      <c r="I28" s="12">
-        <v>1</v>
-      </c>
-      <c r="J28" s="12">
-        <v>3</v>
-      </c>
-      <c r="K28" s="12">
-        <v>4</v>
-      </c>
-      <c r="L28" s="13">
+      <c r="H29" s="12">
+        <v>3</v>
+      </c>
+      <c r="I29" s="12">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12">
+        <v>3</v>
+      </c>
+      <c r="K29" s="12">
+        <v>4</v>
+      </c>
+      <c r="L29" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="M28" s="13" t="str">
+      <c r="M29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="S28" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8">
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="S29" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
         <v>256014</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" s="15" t="s">
+      <c r="B30" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E30" s="16">
         <v>32349</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F30" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>37</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G30" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H29" s="12">
-        <v>4</v>
-      </c>
-      <c r="I29" s="12">
-        <v>1</v>
-      </c>
-      <c r="J29" s="12">
-        <v>4</v>
-      </c>
-      <c r="K29" s="12">
-        <v>4</v>
-      </c>
-      <c r="L29" s="18">
+      <c r="H30" s="12">
+        <v>4</v>
+      </c>
+      <c r="I30" s="12">
+        <v>1</v>
+      </c>
+      <c r="J30" s="12">
+        <v>4</v>
+      </c>
+      <c r="K30" s="12">
+        <v>4</v>
+      </c>
+      <c r="L30" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M29" s="18" t="str">
+      <c r="M30" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="S29" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="S30" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="7">
         <v>443003</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="B31" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E31" s="10">
         <v>28572</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F31" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>48</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G31" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H30" s="12">
-        <v>4</v>
-      </c>
-      <c r="I30" s="12">
-        <v>1</v>
-      </c>
-      <c r="J30" s="12">
-        <v>4</v>
-      </c>
-      <c r="K30" s="12">
+      <c r="H31" s="12">
+        <v>4</v>
+      </c>
+      <c r="I31" s="12">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12">
+        <v>4</v>
+      </c>
+      <c r="K31" s="12">
         <v>5</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L31" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M30" s="13" t="str">
+      <c r="M31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="S30" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8">
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="S31" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
         <v>254057</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D31" s="15" t="s">
+      <c r="B32" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E32" s="16">
         <v>32420</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F32" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>37</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G32" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H31" s="12">
-        <v>4</v>
-      </c>
-      <c r="I31" s="12">
-        <v>1</v>
-      </c>
-      <c r="J31" s="12">
-        <v>4</v>
-      </c>
-      <c r="K31" s="12">
-        <v>4</v>
-      </c>
-      <c r="L31" s="18">
+      <c r="H32" s="12">
+        <v>4</v>
+      </c>
+      <c r="I32" s="12">
+        <v>1</v>
+      </c>
+      <c r="J32" s="12">
+        <v>4</v>
+      </c>
+      <c r="K32" s="12">
+        <v>4</v>
+      </c>
+      <c r="L32" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M31" s="18" t="str">
+      <c r="M32" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="S31" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="7">
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="S32" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="7">
         <v>237011</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" s="9" t="s">
+      <c r="B33" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E33" s="10">
         <v>25410</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F33" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>56</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G33" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H32" s="12">
-        <v>4</v>
-      </c>
-      <c r="I32" s="12">
-        <v>1</v>
-      </c>
-      <c r="J32" s="12">
-        <v>4</v>
-      </c>
-      <c r="K32" s="12">
+      <c r="H33" s="12">
+        <v>4</v>
+      </c>
+      <c r="I33" s="12">
+        <v>1</v>
+      </c>
+      <c r="J33" s="12">
+        <v>4</v>
+      </c>
+      <c r="K33" s="12">
         <v>5</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L33" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M32" s="13" t="str">
+      <c r="M33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="S32" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="S33" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
         <v>267096</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="B34" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E34" s="16">
         <v>32140</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F34" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G34" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="12">
-        <v>4</v>
-      </c>
-      <c r="I33" s="12">
-        <v>3</v>
-      </c>
-      <c r="J33" s="12">
-        <v>4</v>
-      </c>
-      <c r="K33" s="12">
-        <v>4</v>
-      </c>
-      <c r="L33" s="18">
+      <c r="H34" s="12">
+        <v>4</v>
+      </c>
+      <c r="I34" s="12">
+        <v>3</v>
+      </c>
+      <c r="J34" s="12">
+        <v>4</v>
+      </c>
+      <c r="K34" s="12">
+        <v>4</v>
+      </c>
+      <c r="L34" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M33" s="18" t="str">
+      <c r="M34" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="S33" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="7">
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="S34" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
         <v>249048</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="B35" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E35" s="10">
         <v>29299</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F35" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>46</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G35" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H34" s="12">
-        <v>4</v>
-      </c>
-      <c r="I34" s="12">
-        <v>1</v>
-      </c>
-      <c r="J34" s="12">
-        <v>4</v>
-      </c>
-      <c r="K34" s="12">
+      <c r="H35" s="12">
+        <v>4</v>
+      </c>
+      <c r="I35" s="12">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12">
+        <v>4</v>
+      </c>
+      <c r="K35" s="12">
         <v>5</v>
       </c>
-      <c r="L34" s="13">
+      <c r="L35" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M34" s="13" t="str">
+      <c r="M35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="S34" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="S35" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
         <v>269022</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="B36" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E36" s="16">
         <v>30852</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F36" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>42</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G36" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H35" s="12">
-        <v>4</v>
-      </c>
-      <c r="I35" s="12">
-        <v>3</v>
-      </c>
-      <c r="J35" s="12">
-        <v>4</v>
-      </c>
-      <c r="K35" s="12">
-        <v>4</v>
-      </c>
-      <c r="L35" s="18">
+      <c r="H36" s="12">
+        <v>4</v>
+      </c>
+      <c r="I36" s="12">
+        <v>3</v>
+      </c>
+      <c r="J36" s="12">
+        <v>4</v>
+      </c>
+      <c r="K36" s="12">
+        <v>4</v>
+      </c>
+      <c r="L36" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M35" s="18" t="str">
+      <c r="M36" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="S35" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="7">
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="S36" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
         <v>253014</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="B37" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E37" s="10">
         <v>30611</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F37" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>42</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G37" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H36" s="12">
-        <v>3</v>
-      </c>
-      <c r="I36" s="12">
-        <v>1</v>
-      </c>
-      <c r="J36" s="12">
-        <v>3</v>
-      </c>
-      <c r="K36" s="12">
-        <v>4</v>
-      </c>
-      <c r="L36" s="13">
+      <c r="H37" s="12">
+        <v>3</v>
+      </c>
+      <c r="I37" s="12">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12">
+        <v>3</v>
+      </c>
+      <c r="K37" s="12">
+        <v>4</v>
+      </c>
+      <c r="L37" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M36" s="13" t="str">
+      <c r="M37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="S36" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8">
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="S37" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
         <v>248031</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="15" t="s">
+      <c r="B38" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E38" s="16">
         <v>29617</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F38" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>45</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G38" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H37" s="12">
-        <v>3</v>
-      </c>
-      <c r="I37" s="12">
-        <v>1</v>
-      </c>
-      <c r="J37" s="12">
-        <v>4</v>
-      </c>
-      <c r="K37" s="12">
-        <v>4</v>
-      </c>
-      <c r="L37" s="18">
+      <c r="H38" s="12">
+        <v>3</v>
+      </c>
+      <c r="I38" s="12">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12">
+        <v>4</v>
+      </c>
+      <c r="K38" s="12">
+        <v>4</v>
+      </c>
+      <c r="L38" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M37" s="18" t="str">
+      <c r="M38" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="S37" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="S38" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="7">
         <v>251007</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D38" s="9" t="s">
+      <c r="B39" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E39" s="10">
         <v>30522</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F39" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>42</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G39" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H38" s="12">
-        <v>4</v>
-      </c>
-      <c r="I38" s="12">
-        <v>1</v>
-      </c>
-      <c r="J38" s="12">
-        <v>3</v>
-      </c>
-      <c r="K38" s="12">
-        <v>4</v>
-      </c>
-      <c r="L38" s="13">
+      <c r="H39" s="12">
+        <v>4</v>
+      </c>
+      <c r="I39" s="12">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12">
+        <v>3</v>
+      </c>
+      <c r="K39" s="12">
+        <v>4</v>
+      </c>
+      <c r="L39" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M38" s="13" t="str">
+      <c r="M39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="S38" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8">
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="S39" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
         <v>242012</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D39" s="15" t="s">
+      <c r="B40" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E40" s="16">
         <v>28064</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F40" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G40" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H39" s="12">
-        <v>3</v>
-      </c>
-      <c r="I39" s="12">
-        <v>1</v>
-      </c>
-      <c r="J39" s="12">
-        <v>4</v>
-      </c>
-      <c r="K39" s="12">
+      <c r="H40" s="12">
+        <v>3</v>
+      </c>
+      <c r="I40" s="12">
+        <v>1</v>
+      </c>
+      <c r="J40" s="12">
+        <v>4</v>
+      </c>
+      <c r="K40" s="12">
         <v>5</v>
       </c>
-      <c r="L39" s="18">
+      <c r="L40" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M39" s="18" t="str">
+      <c r="M40" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="S39" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="S40" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="7">
         <v>257039</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D40" s="9" t="s">
+      <c r="B41" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E41" s="10">
         <v>32578</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F41" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>37</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G41" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H40" s="12">
-        <v>4</v>
-      </c>
-      <c r="I40" s="12">
-        <v>3</v>
-      </c>
-      <c r="J40" s="12">
-        <v>4</v>
-      </c>
-      <c r="K40" s="12">
-        <v>4</v>
-      </c>
-      <c r="L40" s="13">
+      <c r="H41" s="12">
+        <v>4</v>
+      </c>
+      <c r="I41" s="12">
+        <v>3</v>
+      </c>
+      <c r="J41" s="12">
+        <v>4</v>
+      </c>
+      <c r="K41" s="12">
+        <v>4</v>
+      </c>
+      <c r="L41" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M40" s="13" t="str">
+      <c r="M41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="S40" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8">
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="S41" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
         <v>244023</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D41" s="15" t="s">
+      <c r="B42" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E42" s="16">
         <v>27775</v>
       </c>
-      <c r="F41" s="17">
+      <c r="F42" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>50</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G42" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H41" s="12">
-        <v>3</v>
-      </c>
-      <c r="I41" s="12">
-        <v>1</v>
-      </c>
-      <c r="J41" s="12">
-        <v>3</v>
-      </c>
-      <c r="K41" s="12">
-        <v>4</v>
-      </c>
-      <c r="L41" s="18">
+      <c r="H42" s="12">
+        <v>3</v>
+      </c>
+      <c r="I42" s="12">
+        <v>1</v>
+      </c>
+      <c r="J42" s="12">
+        <v>3</v>
+      </c>
+      <c r="K42" s="12">
+        <v>4</v>
+      </c>
+      <c r="L42" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="M41" s="18" t="str">
+      <c r="M42" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="S41" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="7">
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="S42" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="7">
         <v>241009</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D42" s="9" t="s">
+      <c r="B43" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E43" s="10">
         <v>28315</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F43" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G43" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H42" s="12">
-        <v>4</v>
-      </c>
-      <c r="I42" s="12">
-        <v>3</v>
-      </c>
-      <c r="J42" s="12">
-        <v>4</v>
-      </c>
-      <c r="K42" s="12">
+      <c r="H43" s="12">
+        <v>4</v>
+      </c>
+      <c r="I43" s="12">
+        <v>3</v>
+      </c>
+      <c r="J43" s="12">
+        <v>4</v>
+      </c>
+      <c r="K43" s="12">
         <v>5</v>
       </c>
-      <c r="L42" s="13">
+      <c r="L43" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.3</v>
       </c>
-      <c r="M42" s="13" t="str">
+      <c r="M43" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N42" s="9" t="s">
+      <c r="N43" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="O42" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="S42" s="7" t="s">
+      <c r="S43" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>368001</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8">
-        <v>368001</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="15" t="s">
+      <c r="D44" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E44" s="16">
         <v>30299</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F44" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G44" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H43" s="12">
-        <v>4</v>
-      </c>
-      <c r="I43" s="12">
+      <c r="H44" s="12">
+        <v>4</v>
+      </c>
+      <c r="I44" s="12">
         <v>5</v>
       </c>
-      <c r="J43" s="12">
-        <v>4</v>
-      </c>
-      <c r="K43" s="12">
-        <v>3</v>
-      </c>
-      <c r="L43" s="18">
+      <c r="J44" s="12">
+        <v>4</v>
+      </c>
+      <c r="K44" s="12">
+        <v>3</v>
+      </c>
+      <c r="L44" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="M43" s="18" t="str">
+      <c r="M44" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N43" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="O43" s="15" t="s">
+      <c r="N44" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="O44" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="S43" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="7">
+      <c r="S44" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="7">
         <v>148005</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D44" s="9" t="s">
+      <c r="B45" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E45" s="10">
         <v>27329</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F45" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>51</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G45" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H44" s="12">
-        <v>4</v>
-      </c>
-      <c r="I44" s="12">
-        <v>1</v>
-      </c>
-      <c r="J44" s="12">
-        <v>4</v>
-      </c>
-      <c r="K44" s="12">
-        <v>4</v>
-      </c>
-      <c r="L44" s="13">
+      <c r="H45" s="12">
+        <v>4</v>
+      </c>
+      <c r="I45" s="12">
+        <v>1</v>
+      </c>
+      <c r="J45" s="12">
+        <v>4</v>
+      </c>
+      <c r="K45" s="12">
+        <v>4</v>
+      </c>
+      <c r="L45" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M44" s="13" t="str">
+      <c r="M45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N44" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="S44" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
+      <c r="N45" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="7">
         <v>267071</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B46" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C46" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D46" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E46" s="10">
         <v>28726</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F46" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>47</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G46" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="13" t="str">
+      <c r="H46" s="12">
+        <v>4</v>
+      </c>
+      <c r="I46" s="12">
+        <v>1</v>
+      </c>
+      <c r="J46" s="12">
+        <v>2</v>
+      </c>
+      <c r="K46" s="12">
+        <v>2</v>
+      </c>
+      <c r="L46" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M45" s="13" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="M46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="S45" s="7" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="S46" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8">
+    <row r="47" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
         <v>268051</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B47" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E47" s="16">
         <v>37469</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F47" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>23</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G47" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="18" t="str">
+      <c r="H47" s="12">
+        <v>4</v>
+      </c>
+      <c r="I47" s="12">
+        <v>5</v>
+      </c>
+      <c r="J47" s="12">
+        <v>2</v>
+      </c>
+      <c r="K47" s="12">
+        <v>2</v>
+      </c>
+      <c r="L47" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M46" s="18" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="M47" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="S46" s="8" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
+      <c r="S47" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="7">
+    <row r="48" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="7">
         <v>269032</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B48" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C48" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D48" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E48" s="10">
         <v>30484</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F48" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G48" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="13" t="str">
+      <c r="H48" s="12">
+        <v>4</v>
+      </c>
+      <c r="I48" s="12">
+        <v>3</v>
+      </c>
+      <c r="J48" s="12">
+        <v>2</v>
+      </c>
+      <c r="K48" s="12">
+        <v>2</v>
+      </c>
+      <c r="L48" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M47" s="13" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="M48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="S47" s="7" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="S48" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8">
+    <row r="49" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
         <v>250051</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B49" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C49" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D49" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E49" s="16">
         <v>29866</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F49" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>44</v>
       </c>
-      <c r="G48" s="17">
+      <c r="G49" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="18" t="str">
+      <c r="H49" s="12">
+        <v>4</v>
+      </c>
+      <c r="I49" s="12">
+        <v>1</v>
+      </c>
+      <c r="J49" s="12">
+        <v>2</v>
+      </c>
+      <c r="K49" s="12">
+        <v>2</v>
+      </c>
+      <c r="L49" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M48" s="18" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="M49" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="S48" s="8" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15"/>
+      <c r="S49" s="8" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S48" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S49" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H48 J3:K48" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H49 J3:K49" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I3:I48" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I3:I49" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,3,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O3:O48" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="O3:O49" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Ready Now,Ready in 1 Year,Ready in 3 Years,No Successor"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{47DEDFC0-AFDC-4FD9-AFD0-8574978C772A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A976172-9FE9-49DC-963A-233582E0C4D6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E75FCA-7B5F-4768-BA65-AE4C70D3AA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$49</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="268">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -638,6 +638,210 @@
   </si>
   <si>
     <t>Ready in 3 Years</t>
+  </si>
+  <si>
+    <t>ไชยยันต์ กิจมีรัศมีโยธิน</t>
+  </si>
+  <si>
+    <t>Department Manager - Corporate Information Technology</t>
+  </si>
+  <si>
+    <t>18/04/1966</t>
+  </si>
+  <si>
+    <t>พรพิมล รูปสูง</t>
+  </si>
+  <si>
+    <t>Section Manager - IT Application</t>
+  </si>
+  <si>
+    <t>27/04/1968</t>
+  </si>
+  <si>
+    <t>บัณฑิต มุตติศานต์</t>
+  </si>
+  <si>
+    <t>Section Manager - Corporate Information Technology System</t>
+  </si>
+  <si>
+    <t>27/02/1976</t>
+  </si>
+  <si>
+    <t>ณัฐพร เลิศเมือง</t>
+  </si>
+  <si>
+    <t>Senior Officer - IT</t>
+  </si>
+  <si>
+    <t>15/04/1981</t>
+  </si>
+  <si>
+    <t>นริศ ช่างทำ</t>
+  </si>
+  <si>
+    <t>Senior Programmer - IT</t>
+  </si>
+  <si>
+    <t>19/09/1992</t>
+  </si>
+  <si>
+    <t>กฤษชนก พงษ์วิทยากุล</t>
+  </si>
+  <si>
+    <t>Senior Programmer - E-Commerce</t>
+  </si>
+  <si>
+    <t>03/09/1999</t>
+  </si>
+  <si>
+    <t>พสพร จิรบวรพงศา</t>
+  </si>
+  <si>
+    <t>Senior Officer - IT Support</t>
+  </si>
+  <si>
+    <t>22/01/1990</t>
+  </si>
+  <si>
+    <t>พีร์สรัลณ์ รพินต์รางชาง</t>
+  </si>
+  <si>
+    <t>Support Manager - Data Analytic</t>
+  </si>
+  <si>
+    <t>20/04/1995</t>
+  </si>
+  <si>
+    <t>ธัญญรัตน์ เจริญผล</t>
+  </si>
+  <si>
+    <t>Support Manager - IT</t>
+  </si>
+  <si>
+    <t>02/09/1991</t>
+  </si>
+  <si>
+    <t>กิติพันธ์ ณัฏฐ์มิ่งชื่น</t>
+  </si>
+  <si>
+    <t>Technician - IT Support</t>
+  </si>
+  <si>
+    <t>06/10/1995</t>
+  </si>
+  <si>
+    <t>รังษิยา บรมรัตนไพศาล</t>
+  </si>
+  <si>
+    <t>Financial Controller</t>
+  </si>
+  <si>
+    <t>17/06/1980</t>
+  </si>
+  <si>
+    <t>ณัฐฐา สมานทรัพย์</t>
+  </si>
+  <si>
+    <t>Supervisor - Accounting Receivable</t>
+  </si>
+  <si>
+    <t>09/08/1977</t>
+  </si>
+  <si>
+    <t>ภัทรานิษฐ์ เกิดสุข</t>
+  </si>
+  <si>
+    <t>Senior Officer - Fixed Assets</t>
+  </si>
+  <si>
+    <t>17/03/1975</t>
+  </si>
+  <si>
+    <t>วรวัชร อบเชย</t>
+  </si>
+  <si>
+    <t>Section Manager - Costing</t>
+  </si>
+  <si>
+    <t>28/01/1991</t>
+  </si>
+  <si>
+    <t>วริศรา ปานพุ่ม</t>
+  </si>
+  <si>
+    <t>Senior Officer - Costing</t>
+  </si>
+  <si>
+    <t>01/01/1998</t>
+  </si>
+  <si>
+    <t>ศจี สนทนา</t>
+  </si>
+  <si>
+    <t>Section Manager-Business Control and Treasury</t>
+  </si>
+  <si>
+    <t>28/11/1980</t>
+  </si>
+  <si>
+    <t>สุวิกา บุตรศรี</t>
+  </si>
+  <si>
+    <t>Support Manager - Finance and Account</t>
+  </si>
+  <si>
+    <t>29/11/1994</t>
+  </si>
+  <si>
+    <t>อารีรัตน์ เดชสุขมนัส</t>
+  </si>
+  <si>
+    <t>Supervisor - Accounting Payable</t>
+  </si>
+  <si>
+    <t>24/10/1971</t>
+  </si>
+  <si>
+    <t>ปวีณา ฉิ่งเชิด</t>
+  </si>
+  <si>
+    <t>Officer - Procurement</t>
+  </si>
+  <si>
+    <t>09/04/1996</t>
+  </si>
+  <si>
+    <t>ชนากานต์ รอดสุพรรณ</t>
+  </si>
+  <si>
+    <t>04/12/1998</t>
+  </si>
+  <si>
+    <t>ปิยะวรรณ  ป้องความดี</t>
+  </si>
+  <si>
+    <t>Contract-Procurement</t>
+  </si>
+  <si>
+    <t>14/06/1967</t>
+  </si>
+  <si>
+    <t>อรุณี อุปนันท์</t>
+  </si>
+  <si>
+    <t>Support Manager - Procurement</t>
+  </si>
+  <si>
+    <t>15/03/1981</t>
+  </si>
+  <si>
+    <t>149024 A</t>
+  </si>
+  <si>
+    <t>Acting Procurement Manager</t>
+  </si>
+  <si>
+    <t>17/05/1971</t>
   </si>
 </sst>
 </file>
@@ -898,7 +1102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,43 +1159,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1002,6 +1182,36 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1086,10 +1296,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1281,727 +1487,693 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29" t="s">
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="29"/>
+      <c r="G26" s="32"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="29" t="s">
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="29"/>
+      <c r="G27" s="32"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="32"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="29" t="s">
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="29"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29" t="s">
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="29"/>
+      <c r="G30" s="32"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="26" t="s">
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="26" t="s">
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="34" t="s">
+      <c r="B58" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="26" t="s">
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="26" t="s">
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="24" t="s">
+      <c r="B63" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="24" t="s">
+      <c r="B71" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="24" t="s">
+      <c r="B72" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="24" t="s">
+      <c r="B73" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="24" t="s">
+      <c r="B75" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2015,18 +2187,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2035,7 +2241,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2673,7 +2879,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" s="12">
         <v>1</v>
@@ -4532,17 +4738,1121 @@
         <v>93</v>
       </c>
     </row>
+    <row r="50" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="36">
+        <v>146037</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F50" s="11">
+        <v>60</v>
+      </c>
+      <c r="G50" s="11">
+        <v>5</v>
+      </c>
+      <c r="H50" s="12">
+        <v>5</v>
+      </c>
+      <c r="I50" s="12">
+        <v>3</v>
+      </c>
+      <c r="J50" s="12">
+        <v>4</v>
+      </c>
+      <c r="K50" s="12">
+        <v>5</v>
+      </c>
+      <c r="L50" s="13">
+        <f t="shared" ref="L50:L72" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M50" s="13" t="str">
+        <f t="shared" ref="M50:M72" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="S50" s="7"/>
+    </row>
+    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="37">
+        <v>139013</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="F51" s="17">
+        <v>58</v>
+      </c>
+      <c r="G51" s="17">
+        <v>4</v>
+      </c>
+      <c r="H51" s="12">
+        <v>5</v>
+      </c>
+      <c r="I51" s="12">
+        <v>3</v>
+      </c>
+      <c r="J51" s="12">
+        <v>4</v>
+      </c>
+      <c r="K51" s="12">
+        <v>5</v>
+      </c>
+      <c r="L51" s="18">
+        <f t="shared" si="6"/>
+        <v>3.9</v>
+      </c>
+      <c r="M51" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="S51" s="8"/>
+    </row>
+    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="36">
+        <v>145015</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F52" s="11">
+        <v>50</v>
+      </c>
+      <c r="G52" s="11">
+        <v>2</v>
+      </c>
+      <c r="H52" s="12">
+        <v>4</v>
+      </c>
+      <c r="I52" s="12">
+        <v>3</v>
+      </c>
+      <c r="J52" s="12">
+        <v>4</v>
+      </c>
+      <c r="K52" s="12">
+        <v>4</v>
+      </c>
+      <c r="L52" s="13">
+        <f t="shared" si="6"/>
+        <v>3.3</v>
+      </c>
+      <c r="M52" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
+      <c r="S52" s="7"/>
+    </row>
+    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="37">
+        <v>161005</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F53" s="17">
+        <v>45</v>
+      </c>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="12">
+        <v>2</v>
+      </c>
+      <c r="I53" s="12">
+        <v>1</v>
+      </c>
+      <c r="J53" s="12">
+        <v>3</v>
+      </c>
+      <c r="K53" s="12">
+        <v>3</v>
+      </c>
+      <c r="L53" s="18">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="M53" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="S53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="36">
+        <v>163003</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F54" s="11">
+        <v>34</v>
+      </c>
+      <c r="G54" s="11">
+        <v>1</v>
+      </c>
+      <c r="H54" s="12">
+        <v>3</v>
+      </c>
+      <c r="I54" s="12">
+        <v>3</v>
+      </c>
+      <c r="J54" s="12">
+        <v>2</v>
+      </c>
+      <c r="K54" s="12">
+        <v>3</v>
+      </c>
+      <c r="L54" s="13">
+        <f t="shared" si="6"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M54" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9"/>
+      <c r="S54" s="7"/>
+    </row>
+    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="37">
+        <v>166024</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="F55" s="17">
+        <v>27</v>
+      </c>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="12">
+        <v>2</v>
+      </c>
+      <c r="I55" s="12">
+        <v>3</v>
+      </c>
+      <c r="J55" s="12">
+        <v>2</v>
+      </c>
+      <c r="K55" s="12">
+        <v>3</v>
+      </c>
+      <c r="L55" s="18">
+        <f t="shared" si="6"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M55" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15"/>
+      <c r="S55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="36">
+        <v>167001</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F56" s="11">
+        <v>37</v>
+      </c>
+      <c r="G56" s="11">
+        <v>1</v>
+      </c>
+      <c r="H56" s="12">
+        <v>3</v>
+      </c>
+      <c r="I56" s="12">
+        <v>5</v>
+      </c>
+      <c r="J56" s="12">
+        <v>3</v>
+      </c>
+      <c r="K56" s="12">
+        <v>3</v>
+      </c>
+      <c r="L56" s="13">
+        <f t="shared" si="6"/>
+        <v>3.2</v>
+      </c>
+      <c r="M56" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9"/>
+      <c r="S56" s="7"/>
+    </row>
+    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="37">
+        <v>167012</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="F57" s="17">
+        <v>31</v>
+      </c>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="12">
+        <v>2</v>
+      </c>
+      <c r="I57" s="12">
+        <v>3</v>
+      </c>
+      <c r="J57" s="12">
+        <v>3</v>
+      </c>
+      <c r="K57" s="12">
+        <v>3</v>
+      </c>
+      <c r="L57" s="18">
+        <f t="shared" si="6"/>
+        <v>2.6</v>
+      </c>
+      <c r="M57" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="S57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="36">
+        <v>260001</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F58" s="11">
+        <v>35</v>
+      </c>
+      <c r="G58" s="11">
+        <v>1</v>
+      </c>
+      <c r="H58" s="12">
+        <v>5</v>
+      </c>
+      <c r="I58" s="12">
+        <v>4</v>
+      </c>
+      <c r="J58" s="12">
+        <v>4</v>
+      </c>
+      <c r="K58" s="12">
+        <v>5</v>
+      </c>
+      <c r="L58" s="13">
+        <f t="shared" si="6"/>
+        <v>3.6</v>
+      </c>
+      <c r="M58" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="S58" s="7"/>
+    </row>
+    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="37">
+        <v>267001</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="F59" s="17">
+        <v>31</v>
+      </c>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="12">
+        <v>3</v>
+      </c>
+      <c r="I59" s="12">
+        <v>4</v>
+      </c>
+      <c r="J59" s="12">
+        <v>3</v>
+      </c>
+      <c r="K59" s="12">
+        <v>3</v>
+      </c>
+      <c r="L59" s="18">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="M59" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
+      <c r="P59" s="15"/>
+      <c r="Q59" s="15"/>
+      <c r="S59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="36">
+        <v>160001</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F60" s="11">
+        <v>46</v>
+      </c>
+      <c r="G60" s="11">
+        <v>1</v>
+      </c>
+      <c r="H60" s="12">
+        <v>4</v>
+      </c>
+      <c r="I60" s="12">
+        <v>3</v>
+      </c>
+      <c r="J60" s="12">
+        <v>4</v>
+      </c>
+      <c r="K60" s="12">
+        <v>4</v>
+      </c>
+      <c r="L60" s="13">
+        <f t="shared" si="6"/>
+        <v>3.1</v>
+      </c>
+      <c r="M60" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
+      <c r="S60" s="7"/>
+    </row>
+    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="37">
+        <v>165004</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="F61" s="17">
+        <v>49</v>
+      </c>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="12">
+        <v>4</v>
+      </c>
+      <c r="I61" s="12">
+        <v>3</v>
+      </c>
+      <c r="J61" s="12">
+        <v>3</v>
+      </c>
+      <c r="K61" s="12">
+        <v>4</v>
+      </c>
+      <c r="L61" s="18">
+        <f t="shared" si="6"/>
+        <v>2.8</v>
+      </c>
+      <c r="M61" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
+      <c r="P61" s="15"/>
+      <c r="Q61" s="15"/>
+      <c r="S61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="36">
+        <v>167020</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F62" s="11">
+        <v>51</v>
+      </c>
+      <c r="G62" s="11">
+        <v>2</v>
+      </c>
+      <c r="H62" s="12">
+        <v>3</v>
+      </c>
+      <c r="I62" s="12">
+        <v>3</v>
+      </c>
+      <c r="J62" s="12">
+        <v>3</v>
+      </c>
+      <c r="K62" s="12">
+        <v>4</v>
+      </c>
+      <c r="L62" s="13">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="M62" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
+      <c r="S62" s="7"/>
+    </row>
+    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="37">
+        <v>167029</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="F63" s="17">
+        <v>35</v>
+      </c>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="12">
+        <v>5</v>
+      </c>
+      <c r="I63" s="12">
+        <v>3</v>
+      </c>
+      <c r="J63" s="12">
+        <v>4</v>
+      </c>
+      <c r="K63" s="12">
+        <v>5</v>
+      </c>
+      <c r="L63" s="18">
+        <f t="shared" si="6"/>
+        <v>3.3</v>
+      </c>
+      <c r="M63" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="S63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="36">
+        <v>167032</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" s="11">
+        <v>29</v>
+      </c>
+      <c r="G64" s="11">
+        <v>1</v>
+      </c>
+      <c r="H64" s="12">
+        <v>3</v>
+      </c>
+      <c r="I64" s="12">
+        <v>5</v>
+      </c>
+      <c r="J64" s="12">
+        <v>3</v>
+      </c>
+      <c r="K64" s="12">
+        <v>3</v>
+      </c>
+      <c r="L64" s="13">
+        <f t="shared" si="6"/>
+        <v>3.2</v>
+      </c>
+      <c r="M64" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+      <c r="Q64" s="9"/>
+      <c r="S64" s="7"/>
+    </row>
+    <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="37">
+        <v>168024</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F65" s="17">
+        <v>46</v>
+      </c>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="12">
+        <v>5</v>
+      </c>
+      <c r="I65" s="12">
+        <v>3</v>
+      </c>
+      <c r="J65" s="12">
+        <v>4</v>
+      </c>
+      <c r="K65" s="12">
+        <v>5</v>
+      </c>
+      <c r="L65" s="18">
+        <f t="shared" si="6"/>
+        <v>3.3</v>
+      </c>
+      <c r="M65" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+      <c r="S65" s="8"/>
+    </row>
+    <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="36">
+        <v>168029</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="F66" s="11">
+        <v>32</v>
+      </c>
+      <c r="G66" s="11">
+        <v>1</v>
+      </c>
+      <c r="H66" s="12">
+        <v>4</v>
+      </c>
+      <c r="I66" s="12">
+        <v>5</v>
+      </c>
+      <c r="J66" s="12">
+        <v>4</v>
+      </c>
+      <c r="K66" s="12">
+        <v>4</v>
+      </c>
+      <c r="L66" s="13">
+        <f t="shared" si="6"/>
+        <v>3.7</v>
+      </c>
+      <c r="M66" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
+      <c r="S66" s="7"/>
+    </row>
+    <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="37">
+        <v>337004</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="F67" s="17">
+        <v>55</v>
+      </c>
+      <c r="G67" s="17">
+        <v>3</v>
+      </c>
+      <c r="H67" s="12">
+        <v>3</v>
+      </c>
+      <c r="I67" s="12">
+        <v>1</v>
+      </c>
+      <c r="J67" s="12">
+        <v>3</v>
+      </c>
+      <c r="K67" s="12">
+        <v>4</v>
+      </c>
+      <c r="L67" s="18">
+        <f t="shared" si="6"/>
+        <v>2.6</v>
+      </c>
+      <c r="M67" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="S67" s="8"/>
+    </row>
+    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="36">
+        <v>267085</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F68" s="11">
+        <v>30</v>
+      </c>
+      <c r="G68" s="11">
+        <v>1</v>
+      </c>
+      <c r="H68" s="12">
+        <v>3</v>
+      </c>
+      <c r="I68" s="12">
+        <v>4</v>
+      </c>
+      <c r="J68" s="12">
+        <v>3</v>
+      </c>
+      <c r="K68" s="12">
+        <v>3</v>
+      </c>
+      <c r="L68" s="13">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="M68" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
+      <c r="S68" s="7"/>
+    </row>
+    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="37">
+        <v>268044</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F69" s="17">
+        <v>28</v>
+      </c>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="12">
+        <v>3</v>
+      </c>
+      <c r="I69" s="12">
+        <v>4</v>
+      </c>
+      <c r="J69" s="12">
+        <v>3</v>
+      </c>
+      <c r="K69" s="12">
+        <v>3</v>
+      </c>
+      <c r="L69" s="18">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="M69" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="S69" s="8"/>
+    </row>
+    <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="36">
+        <v>368004</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F70" s="11">
+        <v>59</v>
+      </c>
+      <c r="G70" s="11">
+        <v>4</v>
+      </c>
+      <c r="H70" s="12">
+        <v>4</v>
+      </c>
+      <c r="I70" s="12">
+        <v>3</v>
+      </c>
+      <c r="J70" s="12">
+        <v>4</v>
+      </c>
+      <c r="K70" s="12">
+        <v>4</v>
+      </c>
+      <c r="L70" s="13">
+        <f t="shared" si="6"/>
+        <v>3.7</v>
+      </c>
+      <c r="M70" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+      <c r="P70" s="9"/>
+      <c r="Q70" s="9"/>
+      <c r="S70" s="7"/>
+    </row>
+    <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="37">
+        <v>269040</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="F71" s="17">
+        <v>45</v>
+      </c>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="12">
+        <v>4</v>
+      </c>
+      <c r="I71" s="12">
+        <v>3</v>
+      </c>
+      <c r="J71" s="12">
+        <v>4</v>
+      </c>
+      <c r="K71" s="12">
+        <v>3</v>
+      </c>
+      <c r="L71" s="18">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="M71" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N71" s="15"/>
+      <c r="O71" s="15"/>
+      <c r="P71" s="15"/>
+      <c r="Q71" s="15"/>
+      <c r="S71" s="8"/>
+    </row>
+    <row r="72" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F72" s="11">
+        <v>55</v>
+      </c>
+      <c r="G72" s="11">
+        <v>3</v>
+      </c>
+      <c r="H72" s="12">
+        <v>4</v>
+      </c>
+      <c r="I72" s="12">
+        <v>4</v>
+      </c>
+      <c r="J72" s="12">
+        <v>4</v>
+      </c>
+      <c r="K72" s="12">
+        <v>4</v>
+      </c>
+      <c r="L72" s="13">
+        <f t="shared" si="6"/>
+        <v>3.8</v>
+      </c>
+      <c r="M72" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N72" s="9"/>
+      <c r="O72" s="9"/>
+      <c r="P72" s="9"/>
+      <c r="Q72" s="9"/>
+      <c r="S72" s="7"/>
+    </row>
   </sheetData>
   <autoFilter ref="A2:S49" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H49 J3:K49" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H50 J3:K50" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I3:I49" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I3:I50" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,3,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongkrit.OCEANGLASS\OneDrive - Ocean Glass Public Company Limited\Desktop\Dynamic Org\oceanglass-orgchart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E75FCA-7B5F-4768-BA65-AE4C70D3AA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{81E75FCA-7B5F-4768-BA65-AE4C70D3AA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D481CC-D684-46AB-9D45-0496FB0BBBB7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="คำอธิบาย" sheetId="2" r:id="rId1"/>
@@ -848,7 +848,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -972,8 +972,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1046,6 +1053,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1102,7 +1115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1159,19 +1172,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1183,34 +1220,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1487,693 +1497,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="32"/>
+      <c r="G26" s="29"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32" t="s">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="32"/>
+      <c r="G27" s="29"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32" t="s">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="32"/>
+      <c r="G28" s="29"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32" t="s">
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="32"/>
+      <c r="G29" s="29"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32" t="s">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="29"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="24" t="s">
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="24" t="s">
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="26" t="s">
+      <c r="B58" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="24" t="s">
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="24" t="s">
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="20" t="s">
+      <c r="B74" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2187,52 +2231,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2366,17 +2376,25 @@
         <f t="shared" ref="G3:G49" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
         <v>1</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="13" t="str">
+      <c r="H3" s="12">
+        <v>3</v>
+      </c>
+      <c r="I3" s="12">
+        <v>3</v>
+      </c>
+      <c r="J3" s="12">
+        <v>2</v>
+      </c>
+      <c r="K3" s="12">
+        <v>3</v>
+      </c>
+      <c r="L3" s="13">
         <f t="shared" ref="L3:L49" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
-        <v/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M3" s="13" t="str">
         <f t="shared" ref="M3:M49" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -2410,17 +2428,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="18" t="str">
+      <c r="H4" s="12">
+        <v>4</v>
+      </c>
+      <c r="I4" s="12">
+        <v>3</v>
+      </c>
+      <c r="J4" s="12">
+        <v>3</v>
+      </c>
+      <c r="K4" s="12">
+        <v>3</v>
+      </c>
+      <c r="L4" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.6</v>
       </c>
       <c r="M4" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
@@ -2454,17 +2480,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13" t="str">
+      <c r="H5" s="12">
+        <v>4</v>
+      </c>
+      <c r="I5" s="12">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12">
+        <v>3</v>
+      </c>
+      <c r="K5" s="12">
+        <v>4</v>
+      </c>
+      <c r="L5" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="M5" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -2498,17 +2532,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="18" t="str">
+      <c r="H6" s="12">
+        <v>5</v>
+      </c>
+      <c r="I6" s="12">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12">
+        <v>5</v>
+      </c>
+      <c r="K6" s="12">
+        <v>4</v>
+      </c>
+      <c r="L6" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.2</v>
       </c>
       <c r="M6" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
@@ -2542,17 +2584,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13" t="str">
+      <c r="H7" s="12">
+        <v>3</v>
+      </c>
+      <c r="I7" s="12">
+        <v>3</v>
+      </c>
+      <c r="J7" s="12">
+        <v>2</v>
+      </c>
+      <c r="K7" s="12">
+        <v>3</v>
+      </c>
+      <c r="L7" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
@@ -2586,17 +2636,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13" t="str">
+      <c r="H8" s="12">
+        <v>5</v>
+      </c>
+      <c r="I8" s="12">
+        <v>1</v>
+      </c>
+      <c r="J8" s="12">
+        <v>5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>4</v>
+      </c>
+      <c r="L8" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>3.2</v>
       </c>
       <c r="M8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>High Impact + Low Risk</v>
       </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
@@ -2630,17 +2688,25 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="18" t="str">
+      <c r="H9" s="36">
+        <v>3</v>
+      </c>
+      <c r="I9" s="36">
+        <v>3</v>
+      </c>
+      <c r="J9" s="36">
+        <v>2</v>
+      </c>
+      <c r="K9" s="36">
+        <v>3</v>
+      </c>
+      <c r="L9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M9" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>Low Impact + Low Risk</v>
       </c>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
@@ -3698,7 +3764,7 @@
       </c>
       <c r="F30" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -3854,7 +3920,7 @@
       </c>
       <c r="F33" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G33" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -4166,7 +4232,7 @@
       </c>
       <c r="F39" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -4739,7 +4805,7 @@
       </c>
     </row>
     <row r="50" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="36">
+      <c r="A50" s="7">
         <v>146037</v>
       </c>
       <c r="B50" s="9" t="s">
@@ -4787,7 +4853,7 @@
       <c r="S50" s="7"/>
     </row>
     <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="37">
+      <c r="A51" s="8">
         <v>139013</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -4835,7 +4901,7 @@
       <c r="S51" s="8"/>
     </row>
     <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="36">
+      <c r="A52" s="7">
         <v>145015</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -4883,7 +4949,7 @@
       <c r="S52" s="7"/>
     </row>
     <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="37">
+      <c r="A53" s="8">
         <v>161005</v>
       </c>
       <c r="B53" s="15" t="s">
@@ -4931,7 +4997,7 @@
       <c r="S53" s="8"/>
     </row>
     <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="36">
+      <c r="A54" s="7">
         <v>163003</v>
       </c>
       <c r="B54" s="9" t="s">
@@ -4979,7 +5045,7 @@
       <c r="S54" s="7"/>
     </row>
     <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="37">
+      <c r="A55" s="8">
         <v>166024</v>
       </c>
       <c r="B55" s="15" t="s">
@@ -5027,7 +5093,7 @@
       <c r="S55" s="8"/>
     </row>
     <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="36">
+      <c r="A56" s="7">
         <v>167001</v>
       </c>
       <c r="B56" s="9" t="s">
@@ -5075,7 +5141,7 @@
       <c r="S56" s="7"/>
     </row>
     <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="37">
+      <c r="A57" s="8">
         <v>167012</v>
       </c>
       <c r="B57" s="15" t="s">
@@ -5123,7 +5189,7 @@
       <c r="S57" s="8"/>
     </row>
     <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="36">
+      <c r="A58" s="7">
         <v>260001</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -5171,7 +5237,7 @@
       <c r="S58" s="7"/>
     </row>
     <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="37">
+      <c r="A59" s="8">
         <v>267001</v>
       </c>
       <c r="B59" s="15" t="s">
@@ -5219,7 +5285,7 @@
       <c r="S59" s="8"/>
     </row>
     <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="36">
+      <c r="A60" s="7">
         <v>160001</v>
       </c>
       <c r="B60" s="9" t="s">
@@ -5267,7 +5333,7 @@
       <c r="S60" s="7"/>
     </row>
     <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="37">
+      <c r="A61" s="8">
         <v>165004</v>
       </c>
       <c r="B61" s="15" t="s">
@@ -5315,7 +5381,7 @@
       <c r="S61" s="8"/>
     </row>
     <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="36">
+      <c r="A62" s="7">
         <v>167020</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -5363,7 +5429,7 @@
       <c r="S62" s="7"/>
     </row>
     <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="37">
+      <c r="A63" s="8">
         <v>167029</v>
       </c>
       <c r="B63" s="15" t="s">
@@ -5411,7 +5477,7 @@
       <c r="S63" s="8"/>
     </row>
     <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="36">
+      <c r="A64" s="7">
         <v>167032</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -5459,7 +5525,7 @@
       <c r="S64" s="7"/>
     </row>
     <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="37">
+      <c r="A65" s="8">
         <v>168024</v>
       </c>
       <c r="B65" s="15" t="s">
@@ -5507,7 +5573,7 @@
       <c r="S65" s="8"/>
     </row>
     <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="36">
+      <c r="A66" s="7">
         <v>168029</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -5555,7 +5621,7 @@
       <c r="S66" s="7"/>
     </row>
     <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="37">
+      <c r="A67" s="8">
         <v>337004</v>
       </c>
       <c r="B67" s="15" t="s">
@@ -5603,7 +5669,7 @@
       <c r="S67" s="8"/>
     </row>
     <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="36">
+      <c r="A68" s="7">
         <v>267085</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -5651,7 +5717,7 @@
       <c r="S68" s="7"/>
     </row>
     <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="37">
+      <c r="A69" s="8">
         <v>268044</v>
       </c>
       <c r="B69" s="15" t="s">
@@ -5699,7 +5765,7 @@
       <c r="S69" s="8"/>
     </row>
     <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="36">
+      <c r="A70" s="7">
         <v>368004</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -5747,7 +5813,7 @@
       <c r="S70" s="7"/>
     </row>
     <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="37">
+      <c r="A71" s="8">
         <v>269040</v>
       </c>
       <c r="B71" s="15" t="s">
@@ -5848,7 +5914,7 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H50 J3:K50" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J3:K50 H3:H50" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{81E75FCA-7B5F-4768-BA65-AE4C70D3AA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D481CC-D684-46AB-9D45-0496FB0BBBB7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="คำอธิบาย" sheetId="2" r:id="rId1"/>
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="289">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -842,6 +842,69 @@
   </si>
   <si>
     <t>17/05/1971</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FAIP</t>
+  </si>
+  <si>
+    <t>ยังไม่ได้กรอกคะแนน</t>
+  </si>
+  <si>
+    <t>เวทัส ศฤงฆารสกล</t>
+  </si>
+  <si>
+    <t>Section Manager-Strategic Planning</t>
+  </si>
+  <si>
+    <t>22/05/1991</t>
+  </si>
+  <si>
+    <t>Strategic Planning</t>
+  </si>
+  <si>
+    <t>ธำรงค์ รักถิ่น</t>
+  </si>
+  <si>
+    <t>Department Manager - Quality Management</t>
+  </si>
+  <si>
+    <t>10/12/1984</t>
+  </si>
+  <si>
+    <t>อาณัติ ชนะภัย</t>
+  </si>
+  <si>
+    <t>Executive Director - Customer and Channel Development</t>
+  </si>
+  <si>
+    <t>21/06/1981</t>
+  </si>
+  <si>
+    <t>Executive Director - Manufacturing</t>
+  </si>
+  <si>
+    <t>02/04/1974</t>
+  </si>
+  <si>
+    <t>ณัฐฉวินี นิคมชัยประเสริฐ</t>
+  </si>
+  <si>
+    <t>Executive Director - Marketing</t>
+  </si>
+  <si>
+    <t>07/02/1971</t>
+  </si>
+  <si>
+    <t>เสถียร ศรีใสคำ</t>
+  </si>
+  <si>
+    <t>Executive Director-Finance Accounting, Information Technology and Procurement</t>
+  </si>
+  <si>
+    <t>03/08/1966</t>
   </si>
 </sst>
 </file>
@@ -1169,46 +1232,25 @@
     <xf numFmtId="0" fontId="18" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1220,8 +1262,29 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1497,24 +1560,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="23" t="s">
@@ -1527,146 +1590,146 @@
       <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="23" t="s">
@@ -1679,14 +1742,14 @@
       <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="30" t="s">
@@ -1699,250 +1762,250 @@
       <c r="G25" s="30"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29" t="s">
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="29"/>
+      <c r="G26" s="33"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="29" t="s">
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="29"/>
+      <c r="G27" s="33"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29" t="s">
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="33"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="29" t="s">
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="29"/>
+      <c r="G29" s="33"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29" t="s">
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="29"/>
+      <c r="G30" s="33"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="23" t="s">
@@ -1985,52 +2048,52 @@
       <c r="G55" s="23"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="26" t="s">
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="26" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="34" t="s">
+      <c r="B58" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="26" t="s">
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="26" t="s">
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="23" t="s">
@@ -2043,54 +2106,54 @@
       <c r="G62" s="23"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="24" t="s">
+      <c r="B63" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="23" t="s">
@@ -2103,121 +2166,87 @@
       <c r="G69" s="23"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="24" t="s">
+      <c r="B71" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="24" t="s">
+      <c r="B72" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="24" t="s">
+      <c r="B73" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="24" t="s">
+      <c r="B75" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2231,18 +2260,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2251,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S72"/>
+  <dimension ref="A1:S78"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2275,25 +2338,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="S1" s="5"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -2578,7 +2641,7 @@
       </c>
       <c r="F7" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -2688,16 +2751,16 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H9" s="36">
-        <v>3</v>
-      </c>
-      <c r="I9" s="36">
-        <v>3</v>
-      </c>
-      <c r="J9" s="36">
+      <c r="H9" s="19">
+        <v>3</v>
+      </c>
+      <c r="I9" s="19">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19">
         <v>2</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="19">
         <v>3</v>
       </c>
       <c r="L9" s="18">
@@ -4666,7 +4729,7 @@
       </c>
       <c r="F47" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G47" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -4839,18 +4902,20 @@
         <v>5</v>
       </c>
       <c r="L50" s="13">
-        <f t="shared" ref="L50:L72" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
+        <f t="shared" ref="L50:L73" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="M50" s="13" t="str">
-        <f t="shared" ref="M50:M72" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M50:M73" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + High Risk</v>
       </c>
       <c r="N50" s="9"/>
       <c r="O50" s="9"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
-      <c r="S50" s="7"/>
+      <c r="S50" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
@@ -4898,7 +4963,9 @@
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
       <c r="Q51" s="15"/>
-      <c r="S51" s="8"/>
+      <c r="S51" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
@@ -4946,7 +5013,9 @@
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
-      <c r="S52" s="7"/>
+      <c r="S52" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
@@ -4994,7 +5063,9 @@
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
@@ -5042,7 +5113,9 @@
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
-      <c r="S54" s="7"/>
+      <c r="S54" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
@@ -5090,7 +5163,9 @@
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
       <c r="Q55" s="15"/>
-      <c r="S55" s="8"/>
+      <c r="S55" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
@@ -5138,7 +5213,9 @@
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
-      <c r="S56" s="7"/>
+      <c r="S56" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
@@ -5186,7 +5263,9 @@
       <c r="O57" s="15"/>
       <c r="P57" s="15"/>
       <c r="Q57" s="15"/>
-      <c r="S57" s="8"/>
+      <c r="S57" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
@@ -5234,7 +5313,9 @@
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
-      <c r="S58" s="7"/>
+      <c r="S58" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
@@ -5282,7 +5363,9 @@
       <c r="O59" s="15"/>
       <c r="P59" s="15"/>
       <c r="Q59" s="15"/>
-      <c r="S59" s="8"/>
+      <c r="S59" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
@@ -5330,7 +5413,9 @@
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
-      <c r="S60" s="7"/>
+      <c r="S60" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
@@ -5378,7 +5463,9 @@
       <c r="O61" s="15"/>
       <c r="P61" s="15"/>
       <c r="Q61" s="15"/>
-      <c r="S61" s="8"/>
+      <c r="S61" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
@@ -5426,7 +5513,9 @@
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
-      <c r="S62" s="7"/>
+      <c r="S62" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
@@ -5474,7 +5563,9 @@
       <c r="O63" s="15"/>
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
-      <c r="S63" s="8"/>
+      <c r="S63" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
@@ -5522,7 +5613,9 @@
       <c r="O64" s="9"/>
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
-      <c r="S64" s="7"/>
+      <c r="S64" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8">
@@ -5570,7 +5663,9 @@
       <c r="O65" s="15"/>
       <c r="P65" s="15"/>
       <c r="Q65" s="15"/>
-      <c r="S65" s="8"/>
+      <c r="S65" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
@@ -5618,7 +5713,9 @@
       <c r="O66" s="9"/>
       <c r="P66" s="9"/>
       <c r="Q66" s="9"/>
-      <c r="S66" s="7"/>
+      <c r="S66" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="8">
@@ -5666,7 +5763,9 @@
       <c r="O67" s="15"/>
       <c r="P67" s="15"/>
       <c r="Q67" s="15"/>
-      <c r="S67" s="8"/>
+      <c r="S67" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
@@ -5714,7 +5813,9 @@
       <c r="O68" s="9"/>
       <c r="P68" s="9"/>
       <c r="Q68" s="9"/>
-      <c r="S68" s="7"/>
+      <c r="S68" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="8">
@@ -5762,7 +5863,9 @@
       <c r="O69" s="15"/>
       <c r="P69" s="15"/>
       <c r="Q69" s="15"/>
-      <c r="S69" s="8"/>
+      <c r="S69" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
@@ -5810,7 +5913,9 @@
       <c r="O70" s="9"/>
       <c r="P70" s="9"/>
       <c r="Q70" s="9"/>
-      <c r="S70" s="7"/>
+      <c r="S70" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="8">
@@ -5858,7 +5963,9 @@
       <c r="O71" s="15"/>
       <c r="P71" s="15"/>
       <c r="Q71" s="15"/>
-      <c r="S71" s="8"/>
+      <c r="S71" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="72" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
@@ -5906,10 +6013,378 @@
       <c r="O72" s="9"/>
       <c r="P72" s="9"/>
       <c r="Q72" s="9"/>
-      <c r="S72" s="7"/>
+      <c r="S72" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="7">
+        <v>168016</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F73" s="11">
+        <v>35</v>
+      </c>
+      <c r="G73" s="11">
+        <v>1</v>
+      </c>
+      <c r="H73" s="12">
+        <v>4</v>
+      </c>
+      <c r="I73" s="12">
+        <v>3</v>
+      </c>
+      <c r="J73" s="12">
+        <v>4</v>
+      </c>
+      <c r="K73" s="12">
+        <v>1</v>
+      </c>
+      <c r="L73" s="13">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+      <c r="M73" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="P73" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q73" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R73" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="8">
+        <v>258026</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F74" s="17">
+        <v>42</v>
+      </c>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="12">
+        <v>4</v>
+      </c>
+      <c r="I74" s="12">
+        <v>3</v>
+      </c>
+      <c r="J74" s="12">
+        <v>4</v>
+      </c>
+      <c r="K74" s="12">
+        <v>3</v>
+      </c>
+      <c r="L74" s="18">
+        <f t="shared" ref="L74:L75" si="8">IF(OR(I74="",J74="",K74="",G74=""),"",ROUND(G74*0.2+I74*0.3+J74*0.3+K74*0.2,2))</f>
+        <v>2.9</v>
+      </c>
+      <c r="M74" s="18" t="str">
+        <f t="shared" ref="M74:M75" si="9">IF(OR(H74="",L74=""),"",IF(AND(H74&gt;=4,L74&gt;=3.5),"High Impact + High Risk",IF(AND(H74&gt;=4,L74&lt;3.5),"High Impact + Low Risk",IF(AND(H74&lt;4,L74&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N74" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="O74" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="P74" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q74" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="R74" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S74" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="7">
+        <v>168015</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F75" s="11">
+        <v>45</v>
+      </c>
+      <c r="G75" s="11">
+        <v>1</v>
+      </c>
+      <c r="H75" s="12">
+        <v>5</v>
+      </c>
+      <c r="I75" s="12">
+        <v>3</v>
+      </c>
+      <c r="J75" s="12">
+        <v>3</v>
+      </c>
+      <c r="K75" s="12">
+        <v>3</v>
+      </c>
+      <c r="L75" s="13">
+        <f t="shared" ref="L75:L78" si="10">IF(OR(I75="",J75="",K75="",G75=""),"",ROUND(G75*0.2+I75*0.3+J75*0.3+K75*0.2,2))</f>
+        <v>2.6</v>
+      </c>
+      <c r="M75" s="13" t="str">
+        <f t="shared" ref="M75:M78" si="11">IF(OR(H75="",L75=""),"",IF(AND(H75&gt;=4,L75&gt;=3.5),"High Impact + High Risk",IF(AND(H75&gt;=4,L75&lt;3.5),"High Impact + Low Risk",IF(AND(H75&lt;4,L75&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="P75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q75" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R75" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="8">
+        <v>268029</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F76" s="17">
+        <v>52</v>
+      </c>
+      <c r="G76" s="17">
+        <v>2</v>
+      </c>
+      <c r="H76" s="12">
+        <v>5</v>
+      </c>
+      <c r="I76" s="12">
+        <v>1</v>
+      </c>
+      <c r="J76" s="12">
+        <v>4</v>
+      </c>
+      <c r="K76" s="12">
+        <v>3</v>
+      </c>
+      <c r="L76" s="18">
+        <f t="shared" si="10"/>
+        <v>2.5</v>
+      </c>
+      <c r="M76" s="18" t="str">
+        <f t="shared" si="11"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N76" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="O76" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="P76" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q76" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="R76" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S76" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="7">
+        <v>166006</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F77" s="11">
+        <v>56</v>
+      </c>
+      <c r="G77" s="11">
+        <v>3</v>
+      </c>
+      <c r="H77" s="12">
+        <v>4</v>
+      </c>
+      <c r="I77" s="12">
+        <v>1</v>
+      </c>
+      <c r="J77" s="12">
+        <v>2</v>
+      </c>
+      <c r="K77" s="12">
+        <v>1</v>
+      </c>
+      <c r="L77" s="13">
+        <f t="shared" si="10"/>
+        <v>1.7</v>
+      </c>
+      <c r="M77" s="13" t="str">
+        <f t="shared" si="11"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="P77" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q77" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R77" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="8">
+        <v>169024</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="F78" s="17">
+        <v>60</v>
+      </c>
+      <c r="G78" s="17">
+        <v>5</v>
+      </c>
+      <c r="H78" s="12">
+        <v>5</v>
+      </c>
+      <c r="I78" s="12">
+        <v>1</v>
+      </c>
+      <c r="J78" s="12">
+        <v>2</v>
+      </c>
+      <c r="K78" s="12">
+        <v>1</v>
+      </c>
+      <c r="L78" s="18">
+        <f t="shared" si="10"/>
+        <v>2.1</v>
+      </c>
+      <c r="M78" s="18" t="str">
+        <f t="shared" si="11"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N78" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="O78" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="P78" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q78" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="R78" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S78" s="8" t="s">
+        <v>269</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S49" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S78" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF871B80-3997-4DF4-A055-9DFCE31C65E4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="278">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -872,39 +872,6 @@
   </si>
   <si>
     <t>10/12/1984</t>
-  </si>
-  <si>
-    <t>อาณัติ ชนะภัย</t>
-  </si>
-  <si>
-    <t>Executive Director - Customer and Channel Development</t>
-  </si>
-  <si>
-    <t>21/06/1981</t>
-  </si>
-  <si>
-    <t>Executive Director - Manufacturing</t>
-  </si>
-  <si>
-    <t>02/04/1974</t>
-  </si>
-  <si>
-    <t>ณัฐฉวินี นิคมชัยประเสริฐ</t>
-  </si>
-  <si>
-    <t>Executive Director - Marketing</t>
-  </si>
-  <si>
-    <t>07/02/1971</t>
-  </si>
-  <si>
-    <t>เสถียร ศรีใสคำ</t>
-  </si>
-  <si>
-    <t>Executive Director-Finance Accounting, Information Technology and Procurement</t>
-  </si>
-  <si>
-    <t>03/08/1966</t>
   </si>
 </sst>
 </file>
@@ -1238,19 +1205,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1261,30 +1252,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1560,693 +1527,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="33"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33" t="s">
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="33"/>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33" t="s">
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="33"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33" t="s">
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33" t="s">
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25" t="s">
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="25" t="s">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="25" t="s">
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="25" t="s">
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2260,52 +2261,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2314,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S78"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -6113,11 +6080,11 @@
         <v>3</v>
       </c>
       <c r="L74" s="18">
-        <f t="shared" ref="L74:L75" si="8">IF(OR(I74="",J74="",K74="",G74=""),"",ROUND(G74*0.2+I74*0.3+J74*0.3+K74*0.2,2))</f>
+        <f t="shared" ref="L74" si="8">IF(OR(I74="",J74="",K74="",G74=""),"",ROUND(G74*0.2+I74*0.3+J74*0.3+K74*0.2,2))</f>
         <v>2.9</v>
       </c>
       <c r="M74" s="18" t="str">
-        <f t="shared" ref="M74:M75" si="9">IF(OR(H74="",L74=""),"",IF(AND(H74&gt;=4,L74&gt;=3.5),"High Impact + High Risk",IF(AND(H74&gt;=4,L74&lt;3.5),"High Impact + Low Risk",IF(AND(H74&lt;4,L74&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M74" si="9">IF(OR(H74="",L74=""),"",IF(AND(H74&gt;=4,L74&gt;=3.5),"High Impact + High Risk",IF(AND(H74&gt;=4,L74&lt;3.5),"High Impact + Low Risk",IF(AND(H74&lt;4,L74&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N74" s="15" t="s">
@@ -6139,252 +6106,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="7">
-        <v>168015</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="F75" s="11">
-        <v>45</v>
-      </c>
-      <c r="G75" s="11">
-        <v>1</v>
-      </c>
-      <c r="H75" s="12">
-        <v>5</v>
-      </c>
-      <c r="I75" s="12">
-        <v>3</v>
-      </c>
-      <c r="J75" s="12">
-        <v>3</v>
-      </c>
-      <c r="K75" s="12">
-        <v>3</v>
-      </c>
-      <c r="L75" s="13">
-        <f t="shared" ref="L75:L78" si="10">IF(OR(I75="",J75="",K75="",G75=""),"",ROUND(G75*0.2+I75*0.3+J75*0.3+K75*0.2,2))</f>
-        <v>2.6</v>
-      </c>
-      <c r="M75" s="13" t="str">
-        <f t="shared" ref="M75:M78" si="11">IF(OR(H75="",L75=""),"",IF(AND(H75&gt;=4,L75&gt;=3.5),"High Impact + High Risk",IF(AND(H75&gt;=4,L75&lt;3.5),"High Impact + Low Risk",IF(AND(H75&lt;4,L75&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q75" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="R75" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="8">
-        <v>268029</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="F76" s="17">
-        <v>52</v>
-      </c>
-      <c r="G76" s="17">
-        <v>2</v>
-      </c>
-      <c r="H76" s="12">
-        <v>5</v>
-      </c>
-      <c r="I76" s="12">
-        <v>1</v>
-      </c>
-      <c r="J76" s="12">
-        <v>4</v>
-      </c>
-      <c r="K76" s="12">
-        <v>3</v>
-      </c>
-      <c r="L76" s="18">
-        <f t="shared" si="10"/>
-        <v>2.5</v>
-      </c>
-      <c r="M76" s="18" t="str">
-        <f t="shared" si="11"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N76" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="O76" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="P76" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q76" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="R76" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S76" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="7">
-        <v>166006</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="F77" s="11">
-        <v>56</v>
-      </c>
-      <c r="G77" s="11">
-        <v>3</v>
-      </c>
-      <c r="H77" s="12">
-        <v>4</v>
-      </c>
-      <c r="I77" s="12">
-        <v>1</v>
-      </c>
-      <c r="J77" s="12">
-        <v>2</v>
-      </c>
-      <c r="K77" s="12">
-        <v>1</v>
-      </c>
-      <c r="L77" s="13">
-        <f t="shared" si="10"/>
-        <v>1.7</v>
-      </c>
-      <c r="M77" s="13" t="str">
-        <f t="shared" si="11"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q77" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="R77" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="8">
-        <v>169024</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E78" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="F78" s="17">
-        <v>60</v>
-      </c>
-      <c r="G78" s="17">
-        <v>5</v>
-      </c>
-      <c r="H78" s="12">
-        <v>5</v>
-      </c>
-      <c r="I78" s="12">
-        <v>1</v>
-      </c>
-      <c r="J78" s="12">
-        <v>2</v>
-      </c>
-      <c r="K78" s="12">
-        <v>1</v>
-      </c>
-      <c r="L78" s="18">
-        <f t="shared" si="10"/>
-        <v>2.1</v>
-      </c>
-      <c r="M78" s="18" t="str">
-        <f t="shared" si="11"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N78" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="O78" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="P78" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q78" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="R78" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S78" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:S78" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
